--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1218300</v>
+        <v>1252100</v>
       </c>
       <c r="E8" s="3">
-        <v>1122900</v>
+        <v>1154100</v>
       </c>
       <c r="F8" s="3">
-        <v>1140500</v>
+        <v>1172200</v>
       </c>
       <c r="G8" s="3">
-        <v>1154300</v>
+        <v>1186400</v>
       </c>
       <c r="H8" s="3">
-        <v>1156600</v>
+        <v>1188800</v>
       </c>
       <c r="I8" s="3">
-        <v>1133400</v>
+        <v>1164900</v>
       </c>
       <c r="J8" s="3">
-        <v>1109600</v>
+        <v>1140400</v>
       </c>
       <c r="K8" s="3">
         <v>1170700</v>
@@ -823,25 +823,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>262000</v>
+        <v>269300</v>
       </c>
       <c r="E9" s="3">
-        <v>250700</v>
+        <v>257700</v>
       </c>
       <c r="F9" s="3">
-        <v>204800</v>
+        <v>210500</v>
       </c>
       <c r="G9" s="3">
-        <v>194500</v>
+        <v>199900</v>
       </c>
       <c r="H9" s="3">
-        <v>160000</v>
+        <v>164500</v>
       </c>
       <c r="I9" s="3">
-        <v>171500</v>
+        <v>176200</v>
       </c>
       <c r="J9" s="3">
-        <v>153700</v>
+        <v>158000</v>
       </c>
       <c r="K9" s="3">
         <v>164600</v>
@@ -885,25 +885,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>956300</v>
+        <v>982800</v>
       </c>
       <c r="E10" s="3">
-        <v>872100</v>
+        <v>896400</v>
       </c>
       <c r="F10" s="3">
-        <v>935700</v>
+        <v>961700</v>
       </c>
       <c r="G10" s="3">
-        <v>959700</v>
+        <v>986400</v>
       </c>
       <c r="H10" s="3">
-        <v>996600</v>
+        <v>1024300</v>
       </c>
       <c r="I10" s="3">
-        <v>962000</v>
+        <v>988700</v>
       </c>
       <c r="J10" s="3">
-        <v>955900</v>
+        <v>982500</v>
       </c>
       <c r="K10" s="3">
         <v>1006100</v>
@@ -1095,25 +1095,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="E14" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F14" s="3">
-        <v>-34900</v>
+        <v>-35800</v>
       </c>
       <c r="G14" s="3">
-        <v>5200</v>
+        <v>5400</v>
       </c>
       <c r="H14" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="I14" s="3">
-        <v>-30300</v>
+        <v>-31100</v>
       </c>
       <c r="J14" s="3">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="K14" s="3">
         <v>19400</v>
@@ -1157,25 +1157,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>272100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>276400</v>
+      </c>
+      <c r="F15" s="3">
+        <v>263700</v>
+      </c>
+      <c r="G15" s="3">
+        <v>268500</v>
+      </c>
+      <c r="H15" s="3">
         <v>264700</v>
       </c>
-      <c r="E15" s="3">
-        <v>269000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>256600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>261300</v>
-      </c>
-      <c r="H15" s="3">
-        <v>257500</v>
-      </c>
       <c r="I15" s="3">
-        <v>272300</v>
+        <v>279900</v>
       </c>
       <c r="J15" s="3">
-        <v>251600</v>
+        <v>258600</v>
       </c>
       <c r="K15" s="3">
         <v>359300</v>
@@ -1240,25 +1240,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>919800</v>
+        <v>945400</v>
       </c>
       <c r="E17" s="3">
-        <v>896700</v>
+        <v>921600</v>
       </c>
       <c r="F17" s="3">
-        <v>781100</v>
+        <v>802800</v>
       </c>
       <c r="G17" s="3">
-        <v>810400</v>
+        <v>832900</v>
       </c>
       <c r="H17" s="3">
-        <v>743700</v>
+        <v>764400</v>
       </c>
       <c r="I17" s="3">
-        <v>736000</v>
+        <v>756500</v>
       </c>
       <c r="J17" s="3">
-        <v>714500</v>
+        <v>734300</v>
       </c>
       <c r="K17" s="3">
         <v>857300</v>
@@ -1302,25 +1302,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>298500</v>
+        <v>306800</v>
       </c>
       <c r="E18" s="3">
-        <v>226200</v>
+        <v>232500</v>
       </c>
       <c r="F18" s="3">
-        <v>359400</v>
+        <v>369400</v>
       </c>
       <c r="G18" s="3">
-        <v>343900</v>
+        <v>353500</v>
       </c>
       <c r="H18" s="3">
-        <v>412900</v>
+        <v>424400</v>
       </c>
       <c r="I18" s="3">
-        <v>397400</v>
+        <v>408400</v>
       </c>
       <c r="J18" s="3">
-        <v>395100</v>
+        <v>406100</v>
       </c>
       <c r="K18" s="3">
         <v>313400</v>
@@ -1388,25 +1388,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>166500</v>
+        <v>171100</v>
       </c>
       <c r="E20" s="3">
-        <v>-145400</v>
+        <v>-149400</v>
       </c>
       <c r="F20" s="3">
-        <v>495200</v>
+        <v>509000</v>
       </c>
       <c r="G20" s="3">
-        <v>165100</v>
+        <v>169700</v>
       </c>
       <c r="H20" s="3">
-        <v>34100</v>
+        <v>35100</v>
       </c>
       <c r="I20" s="3">
-        <v>132000</v>
+        <v>135700</v>
       </c>
       <c r="J20" s="3">
-        <v>-15500</v>
+        <v>-15900</v>
       </c>
       <c r="K20" s="3">
         <v>-49200</v>
@@ -1450,25 +1450,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>729700</v>
+        <v>750000</v>
       </c>
       <c r="E21" s="3">
-        <v>349700</v>
+        <v>359500</v>
       </c>
       <c r="F21" s="3">
-        <v>1111200</v>
+        <v>1142100</v>
       </c>
       <c r="G21" s="3">
-        <v>770400</v>
+        <v>791800</v>
       </c>
       <c r="H21" s="3">
-        <v>704400</v>
+        <v>724000</v>
       </c>
       <c r="I21" s="3">
-        <v>801700</v>
+        <v>824000</v>
       </c>
       <c r="J21" s="3">
-        <v>631200</v>
+        <v>648800</v>
       </c>
       <c r="K21" s="3">
         <v>623500</v>
@@ -1512,25 +1512,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>266500</v>
+        <v>273900</v>
       </c>
       <c r="E22" s="3">
-        <v>291700</v>
+        <v>299800</v>
       </c>
       <c r="F22" s="3">
-        <v>325800</v>
+        <v>334800</v>
       </c>
       <c r="G22" s="3">
-        <v>227200</v>
+        <v>233500</v>
       </c>
       <c r="H22" s="3">
-        <v>183100</v>
+        <v>188200</v>
       </c>
       <c r="I22" s="3">
-        <v>95300</v>
+        <v>97900</v>
       </c>
       <c r="J22" s="3">
-        <v>130100</v>
+        <v>133800</v>
       </c>
       <c r="K22" s="3">
         <v>127200</v>
@@ -1574,25 +1574,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>198500</v>
+        <v>204000</v>
       </c>
       <c r="E23" s="3">
-        <v>-210900</v>
+        <v>-216800</v>
       </c>
       <c r="F23" s="3">
-        <v>528900</v>
+        <v>543600</v>
       </c>
       <c r="G23" s="3">
-        <v>281900</v>
+        <v>289700</v>
       </c>
       <c r="H23" s="3">
-        <v>263900</v>
+        <v>271200</v>
       </c>
       <c r="I23" s="3">
-        <v>434100</v>
+        <v>446200</v>
       </c>
       <c r="J23" s="3">
-        <v>249500</v>
+        <v>256400</v>
       </c>
       <c r="K23" s="3">
         <v>137000</v>
@@ -1636,25 +1636,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>53600</v>
+        <v>55100</v>
       </c>
       <c r="E24" s="3">
-        <v>-27200</v>
+        <v>-27900</v>
       </c>
       <c r="F24" s="3">
-        <v>90900</v>
+        <v>93500</v>
       </c>
       <c r="G24" s="3">
-        <v>84100</v>
+        <v>86500</v>
       </c>
       <c r="H24" s="3">
-        <v>532100</v>
+        <v>546900</v>
       </c>
       <c r="I24" s="3">
-        <v>72600</v>
+        <v>74600</v>
       </c>
       <c r="J24" s="3">
-        <v>48500</v>
+        <v>49900</v>
       </c>
       <c r="K24" s="3">
         <v>202600</v>
@@ -1760,25 +1760,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>144900</v>
+        <v>148900</v>
       </c>
       <c r="E26" s="3">
-        <v>-183700</v>
+        <v>-188800</v>
       </c>
       <c r="F26" s="3">
-        <v>437900</v>
+        <v>450100</v>
       </c>
       <c r="G26" s="3">
-        <v>197800</v>
+        <v>203300</v>
       </c>
       <c r="H26" s="3">
-        <v>-268200</v>
+        <v>-275700</v>
       </c>
       <c r="I26" s="3">
-        <v>361500</v>
+        <v>371600</v>
       </c>
       <c r="J26" s="3">
-        <v>201000</v>
+        <v>206600</v>
       </c>
       <c r="K26" s="3">
         <v>-65600</v>
@@ -1822,25 +1822,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>144900</v>
+        <v>148900</v>
       </c>
       <c r="E27" s="3">
-        <v>-183700</v>
+        <v>-188800</v>
       </c>
       <c r="F27" s="3">
-        <v>437900</v>
+        <v>450100</v>
       </c>
       <c r="G27" s="3">
-        <v>197800</v>
+        <v>203300</v>
       </c>
       <c r="H27" s="3">
-        <v>-268200</v>
+        <v>-275700</v>
       </c>
       <c r="I27" s="3">
-        <v>361500</v>
+        <v>371600</v>
       </c>
       <c r="J27" s="3">
-        <v>201000</v>
+        <v>206600</v>
       </c>
       <c r="K27" s="3">
         <v>-65600</v>
@@ -2132,25 +2132,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-166500</v>
+        <v>-171100</v>
       </c>
       <c r="E32" s="3">
-        <v>145400</v>
+        <v>149400</v>
       </c>
       <c r="F32" s="3">
-        <v>-495200</v>
+        <v>-509000</v>
       </c>
       <c r="G32" s="3">
-        <v>-165100</v>
+        <v>-169700</v>
       </c>
       <c r="H32" s="3">
-        <v>-34100</v>
+        <v>-35100</v>
       </c>
       <c r="I32" s="3">
-        <v>-132000</v>
+        <v>-135700</v>
       </c>
       <c r="J32" s="3">
-        <v>15500</v>
+        <v>15900</v>
       </c>
       <c r="K32" s="3">
         <v>49200</v>
@@ -2194,25 +2194,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>144900</v>
+        <v>148900</v>
       </c>
       <c r="E33" s="3">
-        <v>-183700</v>
+        <v>-188800</v>
       </c>
       <c r="F33" s="3">
-        <v>437900</v>
+        <v>450100</v>
       </c>
       <c r="G33" s="3">
-        <v>197800</v>
+        <v>203300</v>
       </c>
       <c r="H33" s="3">
-        <v>-268200</v>
+        <v>-275700</v>
       </c>
       <c r="I33" s="3">
-        <v>361500</v>
+        <v>371600</v>
       </c>
       <c r="J33" s="3">
-        <v>201000</v>
+        <v>206600</v>
       </c>
       <c r="K33" s="3">
         <v>-65600</v>
@@ -2318,25 +2318,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>144900</v>
+        <v>148900</v>
       </c>
       <c r="E35" s="3">
-        <v>-183700</v>
+        <v>-188800</v>
       </c>
       <c r="F35" s="3">
-        <v>437900</v>
+        <v>450100</v>
       </c>
       <c r="G35" s="3">
-        <v>197800</v>
+        <v>203300</v>
       </c>
       <c r="H35" s="3">
-        <v>-268200</v>
+        <v>-275700</v>
       </c>
       <c r="I35" s="3">
-        <v>361500</v>
+        <v>371600</v>
       </c>
       <c r="J35" s="3">
-        <v>201000</v>
+        <v>206600</v>
       </c>
       <c r="K35" s="3">
         <v>-65600</v>
@@ -2495,25 +2495,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1028200</v>
+        <v>1056800</v>
       </c>
       <c r="E41" s="3">
-        <v>422300</v>
+        <v>434000</v>
       </c>
       <c r="F41" s="3">
-        <v>660200</v>
+        <v>678600</v>
       </c>
       <c r="G41" s="3">
-        <v>298900</v>
+        <v>307200</v>
       </c>
       <c r="H41" s="3">
-        <v>813700</v>
+        <v>836300</v>
       </c>
       <c r="I41" s="3">
-        <v>923100</v>
+        <v>948800</v>
       </c>
       <c r="J41" s="3">
-        <v>1115300</v>
+        <v>1146300</v>
       </c>
       <c r="K41" s="3">
         <v>669300</v>
@@ -2619,25 +2619,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>454800</v>
+        <v>467500</v>
       </c>
       <c r="E43" s="3">
-        <v>359000</v>
+        <v>369000</v>
       </c>
       <c r="F43" s="3">
-        <v>362000</v>
+        <v>372100</v>
       </c>
       <c r="G43" s="3">
-        <v>368600</v>
+        <v>378800</v>
       </c>
       <c r="H43" s="3">
-        <v>313900</v>
+        <v>322600</v>
       </c>
       <c r="I43" s="3">
-        <v>292900</v>
+        <v>301100</v>
       </c>
       <c r="J43" s="3">
-        <v>349000</v>
+        <v>358700</v>
       </c>
       <c r="K43" s="3">
         <v>359400</v>
@@ -2681,25 +2681,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>15500</v>
+        <v>15900</v>
       </c>
       <c r="E44" s="3">
-        <v>16300</v>
+        <v>16700</v>
       </c>
       <c r="F44" s="3">
-        <v>29800</v>
+        <v>30600</v>
       </c>
       <c r="G44" s="3">
-        <v>22100</v>
+        <v>22700</v>
       </c>
       <c r="H44" s="3">
-        <v>23400</v>
+        <v>24100</v>
       </c>
       <c r="I44" s="3">
-        <v>22700</v>
+        <v>23300</v>
       </c>
       <c r="J44" s="3">
-        <v>23600</v>
+        <v>24200</v>
       </c>
       <c r="K44" s="3">
         <v>21000</v>
@@ -2743,22 +2743,22 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>38500</v>
+        <v>39500</v>
       </c>
       <c r="E45" s="3">
-        <v>60200</v>
+        <v>61800</v>
       </c>
       <c r="F45" s="3">
-        <v>194500</v>
+        <v>199900</v>
       </c>
       <c r="G45" s="3">
-        <v>72000</v>
+        <v>74000</v>
       </c>
       <c r="H45" s="3">
-        <v>28500</v>
+        <v>29300</v>
       </c>
       <c r="I45" s="3">
-        <v>17900</v>
+        <v>18400</v>
       </c>
       <c r="J45" s="3">
         <v>100</v>
@@ -2805,25 +2805,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1537000</v>
+        <v>1579700</v>
       </c>
       <c r="E46" s="3">
-        <v>857800</v>
+        <v>881600</v>
       </c>
       <c r="F46" s="3">
-        <v>1246600</v>
+        <v>1281200</v>
       </c>
       <c r="G46" s="3">
-        <v>761500</v>
+        <v>782700</v>
       </c>
       <c r="H46" s="3">
-        <v>1179600</v>
+        <v>1212400</v>
       </c>
       <c r="I46" s="3">
-        <v>1256600</v>
+        <v>1291500</v>
       </c>
       <c r="J46" s="3">
-        <v>1488000</v>
+        <v>1529400</v>
       </c>
       <c r="K46" s="3">
         <v>1049800</v>
@@ -2867,25 +2867,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>111400</v>
+        <v>114500</v>
       </c>
       <c r="E47" s="3">
-        <v>114400</v>
+        <v>117600</v>
       </c>
       <c r="F47" s="3">
-        <v>112300</v>
+        <v>115400</v>
       </c>
       <c r="G47" s="3">
-        <v>122000</v>
+        <v>125300</v>
       </c>
       <c r="H47" s="3">
-        <v>105700</v>
+        <v>108600</v>
       </c>
       <c r="I47" s="3">
-        <v>107700</v>
+        <v>110700</v>
       </c>
       <c r="J47" s="3">
-        <v>212100</v>
+        <v>218000</v>
       </c>
       <c r="K47" s="3">
         <v>182400</v>
@@ -2929,25 +2929,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>15909300</v>
+        <v>16351800</v>
       </c>
       <c r="E48" s="3">
-        <v>15595200</v>
+        <v>16028900</v>
       </c>
       <c r="F48" s="3">
-        <v>15285700</v>
+        <v>15710800</v>
       </c>
       <c r="G48" s="3">
-        <v>15070200</v>
+        <v>15489300</v>
       </c>
       <c r="H48" s="3">
-        <v>14833000</v>
+        <v>15245500</v>
       </c>
       <c r="I48" s="3">
-        <v>14637800</v>
+        <v>15044900</v>
       </c>
       <c r="J48" s="3">
-        <v>14451600</v>
+        <v>14853500</v>
       </c>
       <c r="K48" s="3">
         <v>14587800</v>
@@ -2991,25 +2991,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>158700</v>
+        <v>163100</v>
       </c>
       <c r="E49" s="3">
-        <v>176500</v>
+        <v>181400</v>
       </c>
       <c r="F49" s="3">
-        <v>184800</v>
+        <v>190000</v>
       </c>
       <c r="G49" s="3">
-        <v>199500</v>
+        <v>205000</v>
       </c>
       <c r="H49" s="3">
-        <v>211400</v>
+        <v>217300</v>
       </c>
       <c r="I49" s="3">
-        <v>224700</v>
+        <v>230900</v>
       </c>
       <c r="J49" s="3">
-        <v>218100</v>
+        <v>224200</v>
       </c>
       <c r="K49" s="3">
         <v>239500</v>
@@ -3177,25 +3177,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>911000</v>
+        <v>936300</v>
       </c>
       <c r="E52" s="3">
-        <v>1278600</v>
+        <v>1314100</v>
       </c>
       <c r="F52" s="3">
-        <v>1958200</v>
+        <v>2012600</v>
       </c>
       <c r="G52" s="3">
-        <v>1757400</v>
+        <v>1806300</v>
       </c>
       <c r="H52" s="3">
-        <v>1587200</v>
+        <v>1631400</v>
       </c>
       <c r="I52" s="3">
-        <v>1363800</v>
+        <v>1401700</v>
       </c>
       <c r="J52" s="3">
-        <v>1632800</v>
+        <v>1678200</v>
       </c>
       <c r="K52" s="3">
         <v>1738600</v>
@@ -3301,25 +3301,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18627400</v>
+        <v>19145400</v>
       </c>
       <c r="E54" s="3">
-        <v>18022400</v>
+        <v>18523600</v>
       </c>
       <c r="F54" s="3">
-        <v>18787500</v>
+        <v>19310000</v>
       </c>
       <c r="G54" s="3">
-        <v>17910500</v>
+        <v>18408600</v>
       </c>
       <c r="H54" s="3">
-        <v>17916900</v>
+        <v>18415100</v>
       </c>
       <c r="I54" s="3">
-        <v>17590600</v>
+        <v>18079800</v>
       </c>
       <c r="J54" s="3">
-        <v>18002600</v>
+        <v>18503200</v>
       </c>
       <c r="K54" s="3">
         <v>17798100</v>
@@ -3411,25 +3411,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>614300</v>
+        <v>631400</v>
       </c>
       <c r="E57" s="3">
-        <v>467300</v>
+        <v>480300</v>
       </c>
       <c r="F57" s="3">
-        <v>490400</v>
+        <v>504000</v>
       </c>
       <c r="G57" s="3">
-        <v>453800</v>
+        <v>466400</v>
       </c>
       <c r="H57" s="3">
-        <v>472200</v>
+        <v>485300</v>
       </c>
       <c r="I57" s="3">
-        <v>400300</v>
+        <v>411500</v>
       </c>
       <c r="J57" s="3">
-        <v>401200</v>
+        <v>412400</v>
       </c>
       <c r="K57" s="3">
         <v>423800</v>
@@ -3473,25 +3473,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>210200</v>
+        <v>216000</v>
       </c>
       <c r="E58" s="3">
-        <v>218800</v>
+        <v>224900</v>
       </c>
       <c r="F58" s="3">
-        <v>397700</v>
+        <v>408800</v>
       </c>
       <c r="G58" s="3">
-        <v>383100</v>
+        <v>393800</v>
       </c>
       <c r="H58" s="3">
-        <v>819700</v>
+        <v>842500</v>
       </c>
       <c r="I58" s="3">
-        <v>812300</v>
+        <v>834900</v>
       </c>
       <c r="J58" s="3">
-        <v>1058700</v>
+        <v>1088200</v>
       </c>
       <c r="K58" s="3">
         <v>1070900</v>
@@ -3535,25 +3535,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>30900</v>
+        <v>31700</v>
       </c>
       <c r="E59" s="3">
-        <v>28300</v>
+        <v>29100</v>
       </c>
       <c r="F59" s="3">
-        <v>15900</v>
+        <v>16300</v>
       </c>
       <c r="G59" s="3">
-        <v>17400</v>
+        <v>17900</v>
       </c>
       <c r="H59" s="3">
-        <v>20200</v>
+        <v>20800</v>
       </c>
       <c r="I59" s="3">
-        <v>22300</v>
+        <v>23000</v>
       </c>
       <c r="J59" s="3">
-        <v>21100</v>
+        <v>21700</v>
       </c>
       <c r="K59" s="3">
         <v>32100</v>
@@ -3597,25 +3597,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>855400</v>
+        <v>879200</v>
       </c>
       <c r="E60" s="3">
-        <v>714500</v>
+        <v>734300</v>
       </c>
       <c r="F60" s="3">
-        <v>904000</v>
+        <v>929200</v>
       </c>
       <c r="G60" s="3">
-        <v>854300</v>
+        <v>878000</v>
       </c>
       <c r="H60" s="3">
-        <v>1312100</v>
+        <v>1348500</v>
       </c>
       <c r="I60" s="3">
-        <v>1235000</v>
+        <v>1269400</v>
       </c>
       <c r="J60" s="3">
-        <v>1481000</v>
+        <v>1522200</v>
       </c>
       <c r="K60" s="3">
         <v>1526700</v>
@@ -3659,25 +3659,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11139600</v>
+        <v>11449400</v>
       </c>
       <c r="E61" s="3">
-        <v>10246100</v>
+        <v>10531100</v>
       </c>
       <c r="F61" s="3">
-        <v>9854300</v>
+        <v>10128400</v>
       </c>
       <c r="G61" s="3">
-        <v>9516600</v>
+        <v>9781300</v>
       </c>
       <c r="H61" s="3">
-        <v>9679300</v>
+        <v>9948500</v>
       </c>
       <c r="I61" s="3">
-        <v>9673000</v>
+        <v>9942000</v>
       </c>
       <c r="J61" s="3">
-        <v>10039900</v>
+        <v>10319100</v>
       </c>
       <c r="K61" s="3">
         <v>9527700</v>
@@ -3721,25 +3721,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3934900</v>
+        <v>4044400</v>
       </c>
       <c r="E62" s="3">
-        <v>3949600</v>
+        <v>4059400</v>
       </c>
       <c r="F62" s="3">
-        <v>4155000</v>
+        <v>4270600</v>
       </c>
       <c r="G62" s="3">
-        <v>3870700</v>
+        <v>3978300</v>
       </c>
       <c r="H62" s="3">
-        <v>3549000</v>
+        <v>3647700</v>
       </c>
       <c r="I62" s="3">
-        <v>2922400</v>
+        <v>3003600</v>
       </c>
       <c r="J62" s="3">
-        <v>2969100</v>
+        <v>3051700</v>
       </c>
       <c r="K62" s="3">
         <v>2989800</v>
@@ -3969,25 +3969,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>15929900</v>
+        <v>16372900</v>
       </c>
       <c r="E66" s="3">
-        <v>14910200</v>
+        <v>15324800</v>
       </c>
       <c r="F66" s="3">
-        <v>14913400</v>
+        <v>15328100</v>
       </c>
       <c r="G66" s="3">
-        <v>14241600</v>
+        <v>14637600</v>
       </c>
       <c r="H66" s="3">
-        <v>14540300</v>
+        <v>14944700</v>
       </c>
       <c r="I66" s="3">
-        <v>13830300</v>
+        <v>14214900</v>
       </c>
       <c r="J66" s="3">
-        <v>14490100</v>
+        <v>14893000</v>
       </c>
       <c r="K66" s="3">
         <v>14044200</v>
@@ -4303,25 +4303,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2069400</v>
+        <v>2127000</v>
       </c>
       <c r="E72" s="3">
-        <v>2459200</v>
+        <v>2527600</v>
       </c>
       <c r="F72" s="3">
-        <v>2974600</v>
+        <v>3057300</v>
       </c>
       <c r="G72" s="3">
-        <v>2938000</v>
+        <v>3019700</v>
       </c>
       <c r="H72" s="3">
-        <v>2703100</v>
+        <v>2778300</v>
       </c>
       <c r="I72" s="3">
-        <v>3128400</v>
+        <v>3215400</v>
       </c>
       <c r="J72" s="3">
-        <v>2888900</v>
+        <v>2969200</v>
       </c>
       <c r="K72" s="3">
         <v>3107900</v>
@@ -4551,25 +4551,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2697400</v>
+        <v>2772400</v>
       </c>
       <c r="E76" s="3">
-        <v>3112300</v>
+        <v>3198800</v>
       </c>
       <c r="F76" s="3">
-        <v>3874100</v>
+        <v>3981900</v>
       </c>
       <c r="G76" s="3">
-        <v>3669000</v>
+        <v>3771000</v>
       </c>
       <c r="H76" s="3">
-        <v>3376500</v>
+        <v>3470400</v>
       </c>
       <c r="I76" s="3">
-        <v>3760300</v>
+        <v>3864800</v>
       </c>
       <c r="J76" s="3">
-        <v>3512500</v>
+        <v>3610200</v>
       </c>
       <c r="K76" s="3">
         <v>3753900</v>
@@ -4742,25 +4742,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>144900</v>
+        <v>148900</v>
       </c>
       <c r="E81" s="3">
-        <v>-183700</v>
+        <v>-188800</v>
       </c>
       <c r="F81" s="3">
-        <v>437900</v>
+        <v>450100</v>
       </c>
       <c r="G81" s="3">
-        <v>197800</v>
+        <v>203300</v>
       </c>
       <c r="H81" s="3">
-        <v>-268200</v>
+        <v>-275700</v>
       </c>
       <c r="I81" s="3">
-        <v>361500</v>
+        <v>371600</v>
       </c>
       <c r="J81" s="3">
-        <v>201000</v>
+        <v>206600</v>
       </c>
       <c r="K81" s="3">
         <v>-65600</v>
@@ -4828,25 +4828,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>264700</v>
+        <v>272100</v>
       </c>
       <c r="E83" s="3">
-        <v>269000</v>
+        <v>276400</v>
       </c>
       <c r="F83" s="3">
-        <v>256600</v>
+        <v>263700</v>
       </c>
       <c r="G83" s="3">
-        <v>261400</v>
+        <v>268700</v>
       </c>
       <c r="H83" s="3">
-        <v>257400</v>
+        <v>264600</v>
       </c>
       <c r="I83" s="3">
-        <v>272300</v>
+        <v>279900</v>
       </c>
       <c r="J83" s="3">
-        <v>251600</v>
+        <v>258600</v>
       </c>
       <c r="K83" s="3">
         <v>359300</v>
@@ -5200,25 +5200,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>472500</v>
+        <v>485700</v>
       </c>
       <c r="E89" s="3">
-        <v>480000</v>
+        <v>493300</v>
       </c>
       <c r="F89" s="3">
-        <v>497000</v>
+        <v>510800</v>
       </c>
       <c r="G89" s="3">
-        <v>575400</v>
+        <v>591400</v>
       </c>
       <c r="H89" s="3">
-        <v>583800</v>
+        <v>600100</v>
       </c>
       <c r="I89" s="3">
-        <v>571500</v>
+        <v>587400</v>
       </c>
       <c r="J89" s="3">
-        <v>494600</v>
+        <v>508400</v>
       </c>
       <c r="K89" s="3">
         <v>565500</v>
@@ -5472,25 +5472,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-443400</v>
+        <v>-455700</v>
       </c>
       <c r="E94" s="3">
-        <v>-447900</v>
+        <v>-460300</v>
       </c>
       <c r="F94" s="3">
-        <v>-288300</v>
+        <v>-296300</v>
       </c>
       <c r="G94" s="3">
-        <v>-436400</v>
+        <v>-448600</v>
       </c>
       <c r="H94" s="3">
-        <v>-357200</v>
+        <v>-367100</v>
       </c>
       <c r="I94" s="3">
-        <v>-265100</v>
+        <v>-272500</v>
       </c>
       <c r="J94" s="3">
-        <v>-416300</v>
+        <v>-427900</v>
       </c>
       <c r="K94" s="3">
         <v>-364900</v>
@@ -5558,25 +5558,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-256700</v>
+        <v>-263800</v>
       </c>
       <c r="E96" s="3">
-        <v>-128400</v>
+        <v>-132000</v>
       </c>
       <c r="F96" s="3">
-        <v>-245300</v>
+        <v>-252100</v>
       </c>
       <c r="G96" s="3">
-        <v>-122700</v>
+        <v>-126100</v>
       </c>
       <c r="H96" s="3">
-        <v>-243900</v>
+        <v>-250700</v>
       </c>
       <c r="I96" s="3">
-        <v>-121800</v>
+        <v>-125200</v>
       </c>
       <c r="J96" s="3">
-        <v>-240300</v>
+        <v>-247000</v>
       </c>
       <c r="K96" s="3">
         <v>-122700</v>
@@ -5806,25 +5806,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>29000</v>
+        <v>29800</v>
       </c>
       <c r="E100" s="3">
-        <v>-269000</v>
+        <v>-276400</v>
       </c>
       <c r="F100" s="3">
-        <v>163500</v>
+        <v>168100</v>
       </c>
       <c r="G100" s="3">
-        <v>-656300</v>
+        <v>-674500</v>
       </c>
       <c r="H100" s="3">
-        <v>-348200</v>
+        <v>-357900</v>
       </c>
       <c r="I100" s="3">
-        <v>-486600</v>
+        <v>-500100</v>
       </c>
       <c r="J100" s="3">
-        <v>375300</v>
+        <v>385700</v>
       </c>
       <c r="K100" s="3">
         <v>-315800</v>
@@ -5871,7 +5871,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>-1600</v>
+        <v>-1700</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -5930,25 +5930,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>58200</v>
+        <v>59800</v>
       </c>
       <c r="E102" s="3">
-        <v>-238400</v>
+        <v>-245100</v>
       </c>
       <c r="F102" s="3">
-        <v>372200</v>
+        <v>382500</v>
       </c>
       <c r="G102" s="3">
-        <v>-515500</v>
+        <v>-529800</v>
       </c>
       <c r="H102" s="3">
-        <v>-121600</v>
+        <v>-125000</v>
       </c>
       <c r="I102" s="3">
-        <v>-180100</v>
+        <v>-185100</v>
       </c>
       <c r="J102" s="3">
-        <v>453600</v>
+        <v>466200</v>
       </c>
       <c r="K102" s="3">
         <v>-115200</v>

--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1252100</v>
+        <v>1256600</v>
       </c>
       <c r="E8" s="3">
-        <v>1154100</v>
+        <v>1158200</v>
       </c>
       <c r="F8" s="3">
-        <v>1172200</v>
+        <v>1176300</v>
       </c>
       <c r="G8" s="3">
-        <v>1186400</v>
+        <v>1190500</v>
       </c>
       <c r="H8" s="3">
-        <v>1188800</v>
+        <v>1193000</v>
       </c>
       <c r="I8" s="3">
-        <v>1164900</v>
+        <v>1169100</v>
       </c>
       <c r="J8" s="3">
-        <v>1140400</v>
+        <v>1144500</v>
       </c>
       <c r="K8" s="3">
         <v>1170700</v>
@@ -823,25 +823,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>269300</v>
+        <v>270300</v>
       </c>
       <c r="E9" s="3">
-        <v>257700</v>
+        <v>258600</v>
       </c>
       <c r="F9" s="3">
-        <v>210500</v>
+        <v>211300</v>
       </c>
       <c r="G9" s="3">
-        <v>199900</v>
+        <v>200600</v>
       </c>
       <c r="H9" s="3">
-        <v>164500</v>
+        <v>165100</v>
       </c>
       <c r="I9" s="3">
-        <v>176200</v>
+        <v>176800</v>
       </c>
       <c r="J9" s="3">
-        <v>158000</v>
+        <v>158500</v>
       </c>
       <c r="K9" s="3">
         <v>164600</v>
@@ -885,25 +885,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>982800</v>
+        <v>986300</v>
       </c>
       <c r="E10" s="3">
-        <v>896400</v>
+        <v>899600</v>
       </c>
       <c r="F10" s="3">
-        <v>961700</v>
+        <v>965100</v>
       </c>
       <c r="G10" s="3">
-        <v>986400</v>
+        <v>989900</v>
       </c>
       <c r="H10" s="3">
-        <v>1024300</v>
+        <v>1027900</v>
       </c>
       <c r="I10" s="3">
-        <v>988700</v>
+        <v>992200</v>
       </c>
       <c r="J10" s="3">
-        <v>982500</v>
+        <v>985900</v>
       </c>
       <c r="K10" s="3">
         <v>1006100</v>
@@ -1101,7 +1101,7 @@
         <v>3200</v>
       </c>
       <c r="F14" s="3">
-        <v>-35800</v>
+        <v>-36000</v>
       </c>
       <c r="G14" s="3">
         <v>5400</v>
@@ -1110,7 +1110,7 @@
         <v>4000</v>
       </c>
       <c r="I14" s="3">
-        <v>-31100</v>
+        <v>-31200</v>
       </c>
       <c r="J14" s="3">
         <v>3700</v>
@@ -1157,25 +1157,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>272100</v>
+        <v>273100</v>
       </c>
       <c r="E15" s="3">
-        <v>276400</v>
+        <v>277400</v>
       </c>
       <c r="F15" s="3">
-        <v>263700</v>
+        <v>264600</v>
       </c>
       <c r="G15" s="3">
-        <v>268500</v>
+        <v>269500</v>
       </c>
       <c r="H15" s="3">
-        <v>264700</v>
+        <v>265600</v>
       </c>
       <c r="I15" s="3">
-        <v>279900</v>
+        <v>280900</v>
       </c>
       <c r="J15" s="3">
-        <v>258600</v>
+        <v>259500</v>
       </c>
       <c r="K15" s="3">
         <v>359300</v>
@@ -1240,25 +1240,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>945400</v>
+        <v>948700</v>
       </c>
       <c r="E17" s="3">
-        <v>921600</v>
+        <v>924900</v>
       </c>
       <c r="F17" s="3">
-        <v>802800</v>
+        <v>805600</v>
       </c>
       <c r="G17" s="3">
-        <v>832900</v>
+        <v>835800</v>
       </c>
       <c r="H17" s="3">
-        <v>764400</v>
+        <v>767100</v>
       </c>
       <c r="I17" s="3">
-        <v>756500</v>
+        <v>759200</v>
       </c>
       <c r="J17" s="3">
-        <v>734300</v>
+        <v>736900</v>
       </c>
       <c r="K17" s="3">
         <v>857300</v>
@@ -1302,25 +1302,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>306800</v>
+        <v>307900</v>
       </c>
       <c r="E18" s="3">
-        <v>232500</v>
+        <v>233300</v>
       </c>
       <c r="F18" s="3">
-        <v>369400</v>
+        <v>370700</v>
       </c>
       <c r="G18" s="3">
-        <v>353500</v>
+        <v>354700</v>
       </c>
       <c r="H18" s="3">
-        <v>424400</v>
+        <v>425900</v>
       </c>
       <c r="I18" s="3">
-        <v>408400</v>
+        <v>409900</v>
       </c>
       <c r="J18" s="3">
-        <v>406100</v>
+        <v>407600</v>
       </c>
       <c r="K18" s="3">
         <v>313400</v>
@@ -1388,25 +1388,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>171100</v>
+        <v>171700</v>
       </c>
       <c r="E20" s="3">
-        <v>-149400</v>
+        <v>-150000</v>
       </c>
       <c r="F20" s="3">
-        <v>509000</v>
+        <v>510800</v>
       </c>
       <c r="G20" s="3">
-        <v>169700</v>
+        <v>170300</v>
       </c>
       <c r="H20" s="3">
-        <v>35100</v>
+        <v>35200</v>
       </c>
       <c r="I20" s="3">
-        <v>135700</v>
+        <v>136200</v>
       </c>
       <c r="J20" s="3">
-        <v>-15900</v>
+        <v>-16000</v>
       </c>
       <c r="K20" s="3">
         <v>-49200</v>
@@ -1450,25 +1450,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>750000</v>
+        <v>752700</v>
       </c>
       <c r="E21" s="3">
-        <v>359500</v>
+        <v>360700</v>
       </c>
       <c r="F21" s="3">
-        <v>1142100</v>
+        <v>1146100</v>
       </c>
       <c r="G21" s="3">
-        <v>791800</v>
+        <v>794600</v>
       </c>
       <c r="H21" s="3">
-        <v>724000</v>
+        <v>726600</v>
       </c>
       <c r="I21" s="3">
-        <v>824000</v>
+        <v>826900</v>
       </c>
       <c r="J21" s="3">
-        <v>648800</v>
+        <v>651100</v>
       </c>
       <c r="K21" s="3">
         <v>623500</v>
@@ -1512,25 +1512,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>273900</v>
+        <v>274900</v>
       </c>
       <c r="E22" s="3">
-        <v>299800</v>
+        <v>300800</v>
       </c>
       <c r="F22" s="3">
-        <v>334800</v>
+        <v>336000</v>
       </c>
       <c r="G22" s="3">
-        <v>233500</v>
+        <v>234300</v>
       </c>
       <c r="H22" s="3">
-        <v>188200</v>
+        <v>188900</v>
       </c>
       <c r="I22" s="3">
-        <v>97900</v>
+        <v>98300</v>
       </c>
       <c r="J22" s="3">
-        <v>133800</v>
+        <v>134200</v>
       </c>
       <c r="K22" s="3">
         <v>127200</v>
@@ -1574,25 +1574,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>204000</v>
+        <v>204700</v>
       </c>
       <c r="E23" s="3">
-        <v>-216800</v>
+        <v>-217500</v>
       </c>
       <c r="F23" s="3">
-        <v>543600</v>
+        <v>545500</v>
       </c>
       <c r="G23" s="3">
-        <v>289700</v>
+        <v>290700</v>
       </c>
       <c r="H23" s="3">
-        <v>271200</v>
+        <v>272200</v>
       </c>
       <c r="I23" s="3">
-        <v>446200</v>
+        <v>447700</v>
       </c>
       <c r="J23" s="3">
-        <v>256400</v>
+        <v>257300</v>
       </c>
       <c r="K23" s="3">
         <v>137000</v>
@@ -1636,25 +1636,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55100</v>
+        <v>55300</v>
       </c>
       <c r="E24" s="3">
-        <v>-27900</v>
+        <v>-28000</v>
       </c>
       <c r="F24" s="3">
-        <v>93500</v>
+        <v>93800</v>
       </c>
       <c r="G24" s="3">
-        <v>86500</v>
+        <v>86800</v>
       </c>
       <c r="H24" s="3">
-        <v>546900</v>
+        <v>548800</v>
       </c>
       <c r="I24" s="3">
-        <v>74600</v>
+        <v>74900</v>
       </c>
       <c r="J24" s="3">
-        <v>49900</v>
+        <v>50000</v>
       </c>
       <c r="K24" s="3">
         <v>202600</v>
@@ -1760,25 +1760,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>148900</v>
+        <v>149500</v>
       </c>
       <c r="E26" s="3">
-        <v>-188800</v>
+        <v>-189500</v>
       </c>
       <c r="F26" s="3">
-        <v>450100</v>
+        <v>451700</v>
       </c>
       <c r="G26" s="3">
-        <v>203300</v>
+        <v>204000</v>
       </c>
       <c r="H26" s="3">
-        <v>-275700</v>
+        <v>-276700</v>
       </c>
       <c r="I26" s="3">
-        <v>371600</v>
+        <v>372900</v>
       </c>
       <c r="J26" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K26" s="3">
         <v>-65600</v>
@@ -1822,25 +1822,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>148900</v>
+        <v>149500</v>
       </c>
       <c r="E27" s="3">
-        <v>-188800</v>
+        <v>-189500</v>
       </c>
       <c r="F27" s="3">
-        <v>450100</v>
+        <v>451700</v>
       </c>
       <c r="G27" s="3">
-        <v>203300</v>
+        <v>204000</v>
       </c>
       <c r="H27" s="3">
-        <v>-275700</v>
+        <v>-276700</v>
       </c>
       <c r="I27" s="3">
-        <v>371600</v>
+        <v>372900</v>
       </c>
       <c r="J27" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K27" s="3">
         <v>-65600</v>
@@ -2132,25 +2132,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-171100</v>
+        <v>-171700</v>
       </c>
       <c r="E32" s="3">
-        <v>149400</v>
+        <v>150000</v>
       </c>
       <c r="F32" s="3">
-        <v>-509000</v>
+        <v>-510800</v>
       </c>
       <c r="G32" s="3">
-        <v>-169700</v>
+        <v>-170300</v>
       </c>
       <c r="H32" s="3">
-        <v>-35100</v>
+        <v>-35200</v>
       </c>
       <c r="I32" s="3">
-        <v>-135700</v>
+        <v>-136200</v>
       </c>
       <c r="J32" s="3">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="K32" s="3">
         <v>49200</v>
@@ -2194,25 +2194,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>148900</v>
+        <v>149500</v>
       </c>
       <c r="E33" s="3">
-        <v>-188800</v>
+        <v>-189500</v>
       </c>
       <c r="F33" s="3">
-        <v>450100</v>
+        <v>451700</v>
       </c>
       <c r="G33" s="3">
-        <v>203300</v>
+        <v>204000</v>
       </c>
       <c r="H33" s="3">
-        <v>-275700</v>
+        <v>-276700</v>
       </c>
       <c r="I33" s="3">
-        <v>371600</v>
+        <v>372900</v>
       </c>
       <c r="J33" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K33" s="3">
         <v>-65600</v>
@@ -2318,25 +2318,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>148900</v>
+        <v>149500</v>
       </c>
       <c r="E35" s="3">
-        <v>-188800</v>
+        <v>-189500</v>
       </c>
       <c r="F35" s="3">
-        <v>450100</v>
+        <v>451700</v>
       </c>
       <c r="G35" s="3">
-        <v>203300</v>
+        <v>204000</v>
       </c>
       <c r="H35" s="3">
-        <v>-275700</v>
+        <v>-276700</v>
       </c>
       <c r="I35" s="3">
-        <v>371600</v>
+        <v>372900</v>
       </c>
       <c r="J35" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K35" s="3">
         <v>-65600</v>
@@ -2495,25 +2495,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1056800</v>
+        <v>1060500</v>
       </c>
       <c r="E41" s="3">
-        <v>434000</v>
+        <v>435600</v>
       </c>
       <c r="F41" s="3">
-        <v>678600</v>
+        <v>681000</v>
       </c>
       <c r="G41" s="3">
-        <v>307200</v>
+        <v>308300</v>
       </c>
       <c r="H41" s="3">
-        <v>836300</v>
+        <v>839300</v>
       </c>
       <c r="I41" s="3">
-        <v>948800</v>
+        <v>952200</v>
       </c>
       <c r="J41" s="3">
-        <v>1146300</v>
+        <v>1150400</v>
       </c>
       <c r="K41" s="3">
         <v>669300</v>
@@ -2619,25 +2619,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>467500</v>
+        <v>469100</v>
       </c>
       <c r="E43" s="3">
-        <v>369000</v>
+        <v>370300</v>
       </c>
       <c r="F43" s="3">
-        <v>372100</v>
+        <v>373400</v>
       </c>
       <c r="G43" s="3">
-        <v>378800</v>
+        <v>380200</v>
       </c>
       <c r="H43" s="3">
-        <v>322600</v>
+        <v>323700</v>
       </c>
       <c r="I43" s="3">
-        <v>301100</v>
+        <v>302100</v>
       </c>
       <c r="J43" s="3">
-        <v>358700</v>
+        <v>360000</v>
       </c>
       <c r="K43" s="3">
         <v>359400</v>
@@ -2681,25 +2681,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>15900</v>
+        <v>16000</v>
       </c>
       <c r="E44" s="3">
-        <v>16700</v>
+        <v>16800</v>
       </c>
       <c r="F44" s="3">
-        <v>30600</v>
+        <v>30700</v>
       </c>
       <c r="G44" s="3">
-        <v>22700</v>
+        <v>22800</v>
       </c>
       <c r="H44" s="3">
-        <v>24100</v>
+        <v>24200</v>
       </c>
       <c r="I44" s="3">
-        <v>23300</v>
+        <v>23400</v>
       </c>
       <c r="J44" s="3">
-        <v>24200</v>
+        <v>24300</v>
       </c>
       <c r="K44" s="3">
         <v>21000</v>
@@ -2743,19 +2743,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>39500</v>
+        <v>39700</v>
       </c>
       <c r="E45" s="3">
-        <v>61800</v>
+        <v>62100</v>
       </c>
       <c r="F45" s="3">
-        <v>199900</v>
+        <v>200600</v>
       </c>
       <c r="G45" s="3">
-        <v>74000</v>
+        <v>74200</v>
       </c>
       <c r="H45" s="3">
-        <v>29300</v>
+        <v>29400</v>
       </c>
       <c r="I45" s="3">
         <v>18400</v>
@@ -2805,25 +2805,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1579700</v>
+        <v>1585300</v>
       </c>
       <c r="E46" s="3">
-        <v>881600</v>
+        <v>884700</v>
       </c>
       <c r="F46" s="3">
-        <v>1281200</v>
+        <v>1285800</v>
       </c>
       <c r="G46" s="3">
-        <v>782700</v>
+        <v>785400</v>
       </c>
       <c r="H46" s="3">
-        <v>1212400</v>
+        <v>1216700</v>
       </c>
       <c r="I46" s="3">
-        <v>1291500</v>
+        <v>1296100</v>
       </c>
       <c r="J46" s="3">
-        <v>1529400</v>
+        <v>1534800</v>
       </c>
       <c r="K46" s="3">
         <v>1049800</v>
@@ -2867,25 +2867,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>114500</v>
+        <v>114900</v>
       </c>
       <c r="E47" s="3">
-        <v>117600</v>
+        <v>118000</v>
       </c>
       <c r="F47" s="3">
-        <v>115400</v>
+        <v>115800</v>
       </c>
       <c r="G47" s="3">
-        <v>125300</v>
+        <v>125800</v>
       </c>
       <c r="H47" s="3">
-        <v>108600</v>
+        <v>109000</v>
       </c>
       <c r="I47" s="3">
-        <v>110700</v>
+        <v>111100</v>
       </c>
       <c r="J47" s="3">
-        <v>218000</v>
+        <v>218800</v>
       </c>
       <c r="K47" s="3">
         <v>182400</v>
@@ -2929,25 +2929,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16351800</v>
+        <v>16409600</v>
       </c>
       <c r="E48" s="3">
-        <v>16028900</v>
+        <v>16085600</v>
       </c>
       <c r="F48" s="3">
-        <v>15710800</v>
+        <v>15766300</v>
       </c>
       <c r="G48" s="3">
-        <v>15489300</v>
+        <v>15544100</v>
       </c>
       <c r="H48" s="3">
-        <v>15245500</v>
+        <v>15299400</v>
       </c>
       <c r="I48" s="3">
-        <v>15044900</v>
+        <v>15098100</v>
       </c>
       <c r="J48" s="3">
-        <v>14853500</v>
+        <v>14906000</v>
       </c>
       <c r="K48" s="3">
         <v>14587800</v>
@@ -2991,25 +2991,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>163100</v>
+        <v>163700</v>
       </c>
       <c r="E49" s="3">
-        <v>181400</v>
+        <v>182100</v>
       </c>
       <c r="F49" s="3">
-        <v>190000</v>
+        <v>190700</v>
       </c>
       <c r="G49" s="3">
-        <v>205000</v>
+        <v>205800</v>
       </c>
       <c r="H49" s="3">
-        <v>217300</v>
+        <v>218000</v>
       </c>
       <c r="I49" s="3">
-        <v>230900</v>
+        <v>231700</v>
       </c>
       <c r="J49" s="3">
-        <v>224200</v>
+        <v>225000</v>
       </c>
       <c r="K49" s="3">
         <v>239500</v>
@@ -3177,25 +3177,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>936300</v>
+        <v>939600</v>
       </c>
       <c r="E52" s="3">
-        <v>1314100</v>
+        <v>1318800</v>
       </c>
       <c r="F52" s="3">
-        <v>2012600</v>
+        <v>2019700</v>
       </c>
       <c r="G52" s="3">
-        <v>1806300</v>
+        <v>1812700</v>
       </c>
       <c r="H52" s="3">
-        <v>1631400</v>
+        <v>1637100</v>
       </c>
       <c r="I52" s="3">
-        <v>1401700</v>
+        <v>1406700</v>
       </c>
       <c r="J52" s="3">
-        <v>1678200</v>
+        <v>1684100</v>
       </c>
       <c r="K52" s="3">
         <v>1738600</v>
@@ -3301,25 +3301,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19145400</v>
+        <v>19213100</v>
       </c>
       <c r="E54" s="3">
-        <v>18523600</v>
+        <v>18589200</v>
       </c>
       <c r="F54" s="3">
-        <v>19310000</v>
+        <v>19378300</v>
       </c>
       <c r="G54" s="3">
-        <v>18408600</v>
+        <v>18473700</v>
       </c>
       <c r="H54" s="3">
-        <v>18415100</v>
+        <v>18480300</v>
       </c>
       <c r="I54" s="3">
-        <v>18079800</v>
+        <v>18143700</v>
       </c>
       <c r="J54" s="3">
-        <v>18503200</v>
+        <v>18568700</v>
       </c>
       <c r="K54" s="3">
         <v>17798100</v>
@@ -3411,25 +3411,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>631400</v>
+        <v>633700</v>
       </c>
       <c r="E57" s="3">
-        <v>480300</v>
+        <v>482000</v>
       </c>
       <c r="F57" s="3">
-        <v>504000</v>
+        <v>505800</v>
       </c>
       <c r="G57" s="3">
-        <v>466400</v>
+        <v>468100</v>
       </c>
       <c r="H57" s="3">
-        <v>485300</v>
+        <v>487000</v>
       </c>
       <c r="I57" s="3">
-        <v>411500</v>
+        <v>412900</v>
       </c>
       <c r="J57" s="3">
-        <v>412400</v>
+        <v>413800</v>
       </c>
       <c r="K57" s="3">
         <v>423800</v>
@@ -3473,25 +3473,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>216000</v>
+        <v>216800</v>
       </c>
       <c r="E58" s="3">
-        <v>224900</v>
+        <v>225700</v>
       </c>
       <c r="F58" s="3">
-        <v>408800</v>
+        <v>410200</v>
       </c>
       <c r="G58" s="3">
-        <v>393800</v>
+        <v>395100</v>
       </c>
       <c r="H58" s="3">
-        <v>842500</v>
+        <v>845400</v>
       </c>
       <c r="I58" s="3">
-        <v>834900</v>
+        <v>837900</v>
       </c>
       <c r="J58" s="3">
-        <v>1088200</v>
+        <v>1092000</v>
       </c>
       <c r="K58" s="3">
         <v>1070900</v>
@@ -3535,25 +3535,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>31700</v>
+        <v>31900</v>
       </c>
       <c r="E59" s="3">
-        <v>29100</v>
+        <v>29200</v>
       </c>
       <c r="F59" s="3">
-        <v>16300</v>
+        <v>16400</v>
       </c>
       <c r="G59" s="3">
         <v>17900</v>
       </c>
       <c r="H59" s="3">
-        <v>20800</v>
+        <v>20900</v>
       </c>
       <c r="I59" s="3">
         <v>23000</v>
       </c>
       <c r="J59" s="3">
-        <v>21700</v>
+        <v>21800</v>
       </c>
       <c r="K59" s="3">
         <v>32100</v>
@@ -3597,25 +3597,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>879200</v>
+        <v>882300</v>
       </c>
       <c r="E60" s="3">
-        <v>734300</v>
+        <v>736900</v>
       </c>
       <c r="F60" s="3">
-        <v>929200</v>
+        <v>932500</v>
       </c>
       <c r="G60" s="3">
-        <v>878000</v>
+        <v>881100</v>
       </c>
       <c r="H60" s="3">
-        <v>1348500</v>
+        <v>1353300</v>
       </c>
       <c r="I60" s="3">
-        <v>1269400</v>
+        <v>1273900</v>
       </c>
       <c r="J60" s="3">
-        <v>1522200</v>
+        <v>1527600</v>
       </c>
       <c r="K60" s="3">
         <v>1526700</v>
@@ -3659,25 +3659,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11449400</v>
+        <v>11489900</v>
       </c>
       <c r="E61" s="3">
-        <v>10531100</v>
+        <v>10568300</v>
       </c>
       <c r="F61" s="3">
-        <v>10128400</v>
+        <v>10164200</v>
       </c>
       <c r="G61" s="3">
-        <v>9781300</v>
+        <v>9815900</v>
       </c>
       <c r="H61" s="3">
-        <v>9948500</v>
+        <v>9983600</v>
       </c>
       <c r="I61" s="3">
-        <v>9942000</v>
+        <v>9977100</v>
       </c>
       <c r="J61" s="3">
-        <v>10319100</v>
+        <v>10355600</v>
       </c>
       <c r="K61" s="3">
         <v>9527700</v>
@@ -3721,25 +3721,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4044400</v>
+        <v>4058700</v>
       </c>
       <c r="E62" s="3">
-        <v>4059400</v>
+        <v>4073800</v>
       </c>
       <c r="F62" s="3">
-        <v>4270600</v>
+        <v>4285700</v>
       </c>
       <c r="G62" s="3">
-        <v>3978300</v>
+        <v>3992400</v>
       </c>
       <c r="H62" s="3">
-        <v>3647700</v>
+        <v>3660600</v>
       </c>
       <c r="I62" s="3">
-        <v>3003600</v>
+        <v>3014200</v>
       </c>
       <c r="J62" s="3">
-        <v>3051700</v>
+        <v>3062500</v>
       </c>
       <c r="K62" s="3">
         <v>2989800</v>
@@ -3969,25 +3969,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16372900</v>
+        <v>16430800</v>
       </c>
       <c r="E66" s="3">
-        <v>15324800</v>
+        <v>15379000</v>
       </c>
       <c r="F66" s="3">
-        <v>15328100</v>
+        <v>15382300</v>
       </c>
       <c r="G66" s="3">
-        <v>14637600</v>
+        <v>14689400</v>
       </c>
       <c r="H66" s="3">
-        <v>14944700</v>
+        <v>14997500</v>
       </c>
       <c r="I66" s="3">
-        <v>14214900</v>
+        <v>14265200</v>
       </c>
       <c r="J66" s="3">
-        <v>14893000</v>
+        <v>14945700</v>
       </c>
       <c r="K66" s="3">
         <v>14044200</v>
@@ -4303,25 +4303,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2127000</v>
+        <v>2134500</v>
       </c>
       <c r="E72" s="3">
-        <v>2527600</v>
+        <v>2536600</v>
       </c>
       <c r="F72" s="3">
-        <v>3057300</v>
+        <v>3068100</v>
       </c>
       <c r="G72" s="3">
-        <v>3019700</v>
+        <v>3030400</v>
       </c>
       <c r="H72" s="3">
-        <v>2778300</v>
+        <v>2788100</v>
       </c>
       <c r="I72" s="3">
-        <v>3215400</v>
+        <v>3226800</v>
       </c>
       <c r="J72" s="3">
-        <v>2969200</v>
+        <v>2979700</v>
       </c>
       <c r="K72" s="3">
         <v>3107900</v>
@@ -4551,25 +4551,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2772400</v>
+        <v>2782300</v>
       </c>
       <c r="E76" s="3">
-        <v>3198800</v>
+        <v>3210200</v>
       </c>
       <c r="F76" s="3">
-        <v>3981900</v>
+        <v>3996000</v>
       </c>
       <c r="G76" s="3">
-        <v>3771000</v>
+        <v>3784300</v>
       </c>
       <c r="H76" s="3">
-        <v>3470400</v>
+        <v>3482700</v>
       </c>
       <c r="I76" s="3">
-        <v>3864800</v>
+        <v>3878500</v>
       </c>
       <c r="J76" s="3">
-        <v>3610200</v>
+        <v>3623000</v>
       </c>
       <c r="K76" s="3">
         <v>3753900</v>
@@ -4742,25 +4742,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>148900</v>
+        <v>149500</v>
       </c>
       <c r="E81" s="3">
-        <v>-188800</v>
+        <v>-189500</v>
       </c>
       <c r="F81" s="3">
-        <v>450100</v>
+        <v>451700</v>
       </c>
       <c r="G81" s="3">
-        <v>203300</v>
+        <v>204000</v>
       </c>
       <c r="H81" s="3">
-        <v>-275700</v>
+        <v>-276700</v>
       </c>
       <c r="I81" s="3">
-        <v>371600</v>
+        <v>372900</v>
       </c>
       <c r="J81" s="3">
-        <v>206600</v>
+        <v>207300</v>
       </c>
       <c r="K81" s="3">
         <v>-65600</v>
@@ -4828,25 +4828,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>272100</v>
+        <v>273100</v>
       </c>
       <c r="E83" s="3">
-        <v>276400</v>
+        <v>277400</v>
       </c>
       <c r="F83" s="3">
-        <v>263700</v>
+        <v>264600</v>
       </c>
       <c r="G83" s="3">
-        <v>268700</v>
+        <v>269600</v>
       </c>
       <c r="H83" s="3">
-        <v>264600</v>
+        <v>265500</v>
       </c>
       <c r="I83" s="3">
-        <v>279900</v>
+        <v>280900</v>
       </c>
       <c r="J83" s="3">
-        <v>258600</v>
+        <v>259500</v>
       </c>
       <c r="K83" s="3">
         <v>359300</v>
@@ -5200,25 +5200,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>485700</v>
+        <v>487400</v>
       </c>
       <c r="E89" s="3">
-        <v>493300</v>
+        <v>495100</v>
       </c>
       <c r="F89" s="3">
-        <v>510800</v>
+        <v>512600</v>
       </c>
       <c r="G89" s="3">
-        <v>591400</v>
+        <v>593500</v>
       </c>
       <c r="H89" s="3">
-        <v>600100</v>
+        <v>602200</v>
       </c>
       <c r="I89" s="3">
-        <v>587400</v>
+        <v>589500</v>
       </c>
       <c r="J89" s="3">
-        <v>508400</v>
+        <v>510200</v>
       </c>
       <c r="K89" s="3">
         <v>565500</v>
@@ -5472,25 +5472,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-455700</v>
+        <v>-457300</v>
       </c>
       <c r="E94" s="3">
-        <v>-460300</v>
+        <v>-461900</v>
       </c>
       <c r="F94" s="3">
-        <v>-296300</v>
+        <v>-297400</v>
       </c>
       <c r="G94" s="3">
-        <v>-448600</v>
+        <v>-450200</v>
       </c>
       <c r="H94" s="3">
-        <v>-367100</v>
+        <v>-368400</v>
       </c>
       <c r="I94" s="3">
-        <v>-272500</v>
+        <v>-273500</v>
       </c>
       <c r="J94" s="3">
-        <v>-427900</v>
+        <v>-429400</v>
       </c>
       <c r="K94" s="3">
         <v>-364900</v>
@@ -5558,25 +5558,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-263800</v>
+        <v>-264800</v>
       </c>
       <c r="E96" s="3">
-        <v>-132000</v>
+        <v>-132400</v>
       </c>
       <c r="F96" s="3">
-        <v>-252100</v>
+        <v>-253000</v>
       </c>
       <c r="G96" s="3">
-        <v>-126100</v>
+        <v>-126600</v>
       </c>
       <c r="H96" s="3">
-        <v>-250700</v>
+        <v>-251600</v>
       </c>
       <c r="I96" s="3">
-        <v>-125200</v>
+        <v>-125700</v>
       </c>
       <c r="J96" s="3">
-        <v>-247000</v>
+        <v>-247900</v>
       </c>
       <c r="K96" s="3">
         <v>-122700</v>
@@ -5806,25 +5806,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>29800</v>
+        <v>29900</v>
       </c>
       <c r="E100" s="3">
-        <v>-276400</v>
+        <v>-277400</v>
       </c>
       <c r="F100" s="3">
-        <v>168100</v>
+        <v>168700</v>
       </c>
       <c r="G100" s="3">
-        <v>-674500</v>
+        <v>-676900</v>
       </c>
       <c r="H100" s="3">
-        <v>-357900</v>
+        <v>-359200</v>
       </c>
       <c r="I100" s="3">
-        <v>-500100</v>
+        <v>-501900</v>
       </c>
       <c r="J100" s="3">
-        <v>385700</v>
+        <v>387100</v>
       </c>
       <c r="K100" s="3">
         <v>-315800</v>
@@ -5930,25 +5930,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>59800</v>
+        <v>60000</v>
       </c>
       <c r="E102" s="3">
-        <v>-245100</v>
+        <v>-245900</v>
       </c>
       <c r="F102" s="3">
-        <v>382500</v>
+        <v>383900</v>
       </c>
       <c r="G102" s="3">
-        <v>-529800</v>
+        <v>-531700</v>
       </c>
       <c r="H102" s="3">
-        <v>-125000</v>
+        <v>-125400</v>
       </c>
       <c r="I102" s="3">
-        <v>-185100</v>
+        <v>-185800</v>
       </c>
       <c r="J102" s="3">
-        <v>466200</v>
+        <v>467800</v>
       </c>
       <c r="K102" s="3">
         <v>-115200</v>

--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
   <si>
     <t>UUGRY</t>
   </si>
@@ -656,293 +656,306 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43373</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43190</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43008</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42825</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42643</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42460</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42277</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42094</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1256600</v>
+        <v>1269600</v>
       </c>
       <c r="E8" s="3">
-        <v>1158200</v>
+        <v>1288600</v>
       </c>
       <c r="F8" s="3">
-        <v>1176300</v>
+        <v>1187700</v>
       </c>
       <c r="G8" s="3">
-        <v>1190500</v>
+        <v>1206300</v>
       </c>
       <c r="H8" s="3">
-        <v>1193000</v>
+        <v>1220900</v>
       </c>
       <c r="I8" s="3">
-        <v>1169100</v>
+        <v>1223400</v>
       </c>
       <c r="J8" s="3">
+        <v>1198800</v>
+      </c>
+      <c r="K8" s="3">
         <v>1144500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1170700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1160800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1056600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1117900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1172600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1239600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1124000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1050600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1138700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1117800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1133500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1131600</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>270300</v>
+        <v>274100</v>
       </c>
       <c r="E9" s="3">
-        <v>258600</v>
+        <v>277100</v>
       </c>
       <c r="F9" s="3">
-        <v>211300</v>
+        <v>265200</v>
       </c>
       <c r="G9" s="3">
-        <v>200600</v>
+        <v>216600</v>
       </c>
       <c r="H9" s="3">
-        <v>165100</v>
+        <v>205800</v>
       </c>
       <c r="I9" s="3">
-        <v>176800</v>
+        <v>169300</v>
       </c>
       <c r="J9" s="3">
+        <v>181300</v>
+      </c>
+      <c r="K9" s="3">
         <v>158500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>164600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>149800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>152600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>161600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>167200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>159600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>153600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>153500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>170600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>162100</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>986300</v>
+        <v>995400</v>
       </c>
       <c r="E10" s="3">
-        <v>899600</v>
+        <v>1011400</v>
       </c>
       <c r="F10" s="3">
-        <v>965100</v>
+        <v>922500</v>
       </c>
       <c r="G10" s="3">
-        <v>989900</v>
+        <v>989700</v>
       </c>
       <c r="H10" s="3">
-        <v>1027900</v>
+        <v>1015100</v>
       </c>
       <c r="I10" s="3">
-        <v>992200</v>
+        <v>1054100</v>
       </c>
       <c r="J10" s="3">
+        <v>1017500</v>
+      </c>
+      <c r="K10" s="3">
         <v>985900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1006100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1011000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>904000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>956300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1005400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1080000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>970400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>897100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>968100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>955700</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -965,8 +978,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -997,11 +1011,11 @@
       <c r="L12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N12" s="3">
         <v>1400</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>5</v>
@@ -1015,11 +1029,11 @@
       <c r="R12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S12" s="3">
+      <c r="S12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T12" s="3">
         <v>3000</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>5</v>
@@ -1027,8 +1041,11 @@
       <c r="V12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1089,132 +1106,141 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>5400</v>
+        <v>3300</v>
       </c>
       <c r="E14" s="3">
-        <v>3200</v>
+        <v>5500</v>
       </c>
       <c r="F14" s="3">
-        <v>-36000</v>
+        <v>3300</v>
       </c>
       <c r="G14" s="3">
-        <v>5400</v>
+        <v>-36900</v>
       </c>
       <c r="H14" s="3">
-        <v>4000</v>
+        <v>5500</v>
       </c>
       <c r="I14" s="3">
-        <v>-31200</v>
+        <v>4100</v>
       </c>
       <c r="J14" s="3">
+        <v>-32000</v>
+      </c>
+      <c r="K14" s="3">
         <v>3700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>59700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>15500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>22200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-13400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>33900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>11100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>273100</v>
+        <v>295800</v>
       </c>
       <c r="E15" s="3">
-        <v>277400</v>
+        <v>280000</v>
       </c>
       <c r="F15" s="3">
-        <v>264600</v>
+        <v>284500</v>
       </c>
       <c r="G15" s="3">
-        <v>269500</v>
+        <v>271400</v>
       </c>
       <c r="H15" s="3">
-        <v>265600</v>
+        <v>276300</v>
       </c>
       <c r="I15" s="3">
-        <v>280900</v>
+        <v>272400</v>
       </c>
       <c r="J15" s="3">
+        <v>288000</v>
+      </c>
+      <c r="K15" s="3">
         <v>259500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>359300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>247300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>236800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>233000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>261200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>262200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>246900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>219200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>232900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>241400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>236900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1234,132 +1260,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>948700</v>
+        <v>955200</v>
       </c>
       <c r="E17" s="3">
-        <v>924900</v>
+        <v>972900</v>
       </c>
       <c r="F17" s="3">
-        <v>805600</v>
+        <v>948500</v>
       </c>
       <c r="G17" s="3">
-        <v>835800</v>
+        <v>826200</v>
       </c>
       <c r="H17" s="3">
-        <v>767100</v>
+        <v>857100</v>
       </c>
       <c r="I17" s="3">
-        <v>759200</v>
+        <v>786700</v>
       </c>
       <c r="J17" s="3">
+        <v>778500</v>
+      </c>
+      <c r="K17" s="3">
         <v>736900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>857300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>685500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>710200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>704200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>770800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>756000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>723700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>650900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>760900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>754800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>721600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>307900</v>
+        <v>314400</v>
       </c>
       <c r="E18" s="3">
-        <v>233300</v>
+        <v>315700</v>
       </c>
       <c r="F18" s="3">
-        <v>370700</v>
+        <v>239200</v>
       </c>
       <c r="G18" s="3">
-        <v>354700</v>
+        <v>380100</v>
       </c>
       <c r="H18" s="3">
-        <v>425900</v>
+        <v>363700</v>
       </c>
       <c r="I18" s="3">
-        <v>409900</v>
+        <v>436700</v>
       </c>
       <c r="J18" s="3">
+        <v>420300</v>
+      </c>
+      <c r="K18" s="3">
         <v>407600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>313400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>475200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>346500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>413700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>401800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>483700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>400300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>399700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>377700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>363000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>411900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>448400</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1382,318 +1415,334 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>171700</v>
+        <v>-84800</v>
       </c>
       <c r="E20" s="3">
-        <v>-150000</v>
+        <v>176100</v>
       </c>
       <c r="F20" s="3">
-        <v>510800</v>
+        <v>-153800</v>
       </c>
       <c r="G20" s="3">
-        <v>170300</v>
+        <v>523800</v>
       </c>
       <c r="H20" s="3">
-        <v>35200</v>
+        <v>174700</v>
       </c>
       <c r="I20" s="3">
-        <v>136200</v>
+        <v>36100</v>
       </c>
       <c r="J20" s="3">
+        <v>139600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-16000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-49200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-70200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-25300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>67000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>22900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>63400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>116400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-57000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-75500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>54300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-112200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>752700</v>
+        <v>525400</v>
       </c>
       <c r="E21" s="3">
-        <v>360700</v>
+        <v>771800</v>
       </c>
       <c r="F21" s="3">
-        <v>1146100</v>
+        <v>369900</v>
       </c>
       <c r="G21" s="3">
-        <v>794600</v>
+        <v>1175300</v>
       </c>
       <c r="H21" s="3">
-        <v>726600</v>
+        <v>814900</v>
       </c>
       <c r="I21" s="3">
-        <v>826900</v>
+        <v>745100</v>
       </c>
       <c r="J21" s="3">
+        <v>847900</v>
+      </c>
+      <c r="K21" s="3">
         <v>651100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>623500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>652300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>558000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>713600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>685800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>809300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>763500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>561900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>535200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>658700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>536600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>648900</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>274900</v>
+        <v>216500</v>
       </c>
       <c r="E22" s="3">
-        <v>300800</v>
+        <v>281900</v>
       </c>
       <c r="F22" s="3">
-        <v>336000</v>
+        <v>308500</v>
       </c>
       <c r="G22" s="3">
-        <v>234300</v>
+        <v>344600</v>
       </c>
       <c r="H22" s="3">
-        <v>188900</v>
+        <v>240300</v>
       </c>
       <c r="I22" s="3">
-        <v>98300</v>
+        <v>193700</v>
       </c>
       <c r="J22" s="3">
+        <v>100800</v>
+      </c>
+      <c r="K22" s="3">
         <v>134200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>127200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>162900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>114300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>164000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>165800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>204200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>141600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>147500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>122300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>136000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>119400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>204700</v>
+        <v>13100</v>
       </c>
       <c r="E23" s="3">
-        <v>-217500</v>
+        <v>210000</v>
       </c>
       <c r="F23" s="3">
-        <v>545500</v>
+        <v>-223100</v>
       </c>
       <c r="G23" s="3">
-        <v>290700</v>
+        <v>559400</v>
       </c>
       <c r="H23" s="3">
-        <v>272200</v>
+        <v>298100</v>
       </c>
       <c r="I23" s="3">
-        <v>447700</v>
+        <v>279100</v>
       </c>
       <c r="J23" s="3">
+        <v>459100</v>
+      </c>
+      <c r="K23" s="3">
         <v>257300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>137000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>242100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>206900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>316700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>258800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>342900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>375100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>195100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>179900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>281200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>180300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>269500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>55300</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>-28000</v>
+        <v>56700</v>
       </c>
       <c r="F24" s="3">
-        <v>93800</v>
+        <v>-28700</v>
       </c>
       <c r="G24" s="3">
-        <v>86800</v>
+        <v>96200</v>
       </c>
       <c r="H24" s="3">
-        <v>548800</v>
+        <v>89000</v>
       </c>
       <c r="I24" s="3">
-        <v>74900</v>
+        <v>562800</v>
       </c>
       <c r="J24" s="3">
+        <v>76800</v>
+      </c>
+      <c r="K24" s="3">
         <v>50000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>202600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>45300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>30100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>57500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>44500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>63500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>69600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-54400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-114400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>57000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>37500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>55200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1754,132 +1803,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>149500</v>
+        <v>13300</v>
       </c>
       <c r="E26" s="3">
-        <v>-189500</v>
+        <v>153300</v>
       </c>
       <c r="F26" s="3">
-        <v>451700</v>
+        <v>-194300</v>
       </c>
       <c r="G26" s="3">
-        <v>204000</v>
+        <v>463200</v>
       </c>
       <c r="H26" s="3">
-        <v>-276700</v>
+        <v>209200</v>
       </c>
       <c r="I26" s="3">
-        <v>372900</v>
+        <v>-283700</v>
       </c>
       <c r="J26" s="3">
+        <v>382400</v>
+      </c>
+      <c r="K26" s="3">
         <v>207300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-65600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>196800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>176700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>259200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>214400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>279300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>305500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>249500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>294300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>224200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>142700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>149500</v>
+        <v>13300</v>
       </c>
       <c r="E27" s="3">
-        <v>-189500</v>
+        <v>153300</v>
       </c>
       <c r="F27" s="3">
-        <v>451700</v>
+        <v>-194300</v>
       </c>
       <c r="G27" s="3">
-        <v>204000</v>
+        <v>463200</v>
       </c>
       <c r="H27" s="3">
-        <v>-276700</v>
+        <v>209200</v>
       </c>
       <c r="I27" s="3">
-        <v>372900</v>
+        <v>-283700</v>
       </c>
       <c r="J27" s="3">
+        <v>382400</v>
+      </c>
+      <c r="K27" s="3">
         <v>207300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-65600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>196800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>176700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>259200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>214400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>279300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>305500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>249500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>294300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>224200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>142700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1940,8 +1998,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1984,8 +2045,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>5</v>
@@ -1996,14 +2057,17 @@
       <c r="T29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2064,8 +2128,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2126,132 +2193,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-171700</v>
+        <v>84800</v>
       </c>
       <c r="E32" s="3">
-        <v>150000</v>
+        <v>-176100</v>
       </c>
       <c r="F32" s="3">
-        <v>-510800</v>
+        <v>153800</v>
       </c>
       <c r="G32" s="3">
-        <v>-170300</v>
+        <v>-523800</v>
       </c>
       <c r="H32" s="3">
-        <v>-35200</v>
+        <v>-174700</v>
       </c>
       <c r="I32" s="3">
-        <v>-136200</v>
+        <v>-36100</v>
       </c>
       <c r="J32" s="3">
+        <v>-139600</v>
+      </c>
+      <c r="K32" s="3">
         <v>16000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>49200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>70200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>25300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-67000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-22900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-116400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>57000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>75500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-54300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>112200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>149500</v>
+        <v>13300</v>
       </c>
       <c r="E33" s="3">
-        <v>-189500</v>
+        <v>153300</v>
       </c>
       <c r="F33" s="3">
-        <v>451700</v>
+        <v>-194300</v>
       </c>
       <c r="G33" s="3">
-        <v>204000</v>
+        <v>463200</v>
       </c>
       <c r="H33" s="3">
-        <v>-276700</v>
+        <v>209200</v>
       </c>
       <c r="I33" s="3">
-        <v>372900</v>
+        <v>-283700</v>
       </c>
       <c r="J33" s="3">
+        <v>382400</v>
+      </c>
+      <c r="K33" s="3">
         <v>207300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-65600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>196800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>176700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>259200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>214400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>279300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>305500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>249500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>294300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>224200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>142700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2312,137 +2388,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>149500</v>
+        <v>13300</v>
       </c>
       <c r="E35" s="3">
-        <v>-189500</v>
+        <v>153300</v>
       </c>
       <c r="F35" s="3">
-        <v>451700</v>
+        <v>-194300</v>
       </c>
       <c r="G35" s="3">
-        <v>204000</v>
+        <v>463200</v>
       </c>
       <c r="H35" s="3">
-        <v>-276700</v>
+        <v>209200</v>
       </c>
       <c r="I35" s="3">
-        <v>372900</v>
+        <v>-283700</v>
       </c>
       <c r="J35" s="3">
+        <v>382400</v>
+      </c>
+      <c r="K35" s="3">
         <v>207300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-65600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>196800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>176700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>259200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>214400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>279300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>305500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>249500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>294300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>224200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>142700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43373</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43190</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43008</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42825</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42643</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42460</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42277</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42094</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2465,8 +2550,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2489,70 +2575,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1060500</v>
+        <v>1836200</v>
       </c>
       <c r="E41" s="3">
-        <v>435600</v>
+        <v>1087600</v>
       </c>
       <c r="F41" s="3">
-        <v>681000</v>
+        <v>446700</v>
       </c>
       <c r="G41" s="3">
-        <v>308300</v>
+        <v>698400</v>
       </c>
       <c r="H41" s="3">
-        <v>839300</v>
+        <v>316100</v>
       </c>
       <c r="I41" s="3">
-        <v>952200</v>
+        <v>860700</v>
       </c>
       <c r="J41" s="3">
+        <v>976400</v>
+      </c>
+      <c r="K41" s="3">
         <v>1150400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>669300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>771300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>397400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>316700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>695500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>124000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>327300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>292400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>278600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>464900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>321300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>145600</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2613,442 +2703,466 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>469100</v>
+        <v>429000</v>
       </c>
       <c r="E43" s="3">
-        <v>370300</v>
+        <v>481100</v>
       </c>
       <c r="F43" s="3">
-        <v>373400</v>
+        <v>379800</v>
       </c>
       <c r="G43" s="3">
-        <v>380200</v>
+        <v>382900</v>
       </c>
       <c r="H43" s="3">
-        <v>323700</v>
+        <v>389900</v>
       </c>
       <c r="I43" s="3">
-        <v>302100</v>
+        <v>332000</v>
       </c>
       <c r="J43" s="3">
+        <v>309800</v>
+      </c>
+      <c r="K43" s="3">
         <v>360000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>359400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>360200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>311400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>355200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>389200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>413500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>410800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>424900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>479200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>495500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>465200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>464300</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>16000</v>
+        <v>28200</v>
       </c>
       <c r="E44" s="3">
-        <v>16800</v>
+        <v>16400</v>
       </c>
       <c r="F44" s="3">
-        <v>30700</v>
+        <v>17200</v>
       </c>
       <c r="G44" s="3">
-        <v>22800</v>
+        <v>31500</v>
       </c>
       <c r="H44" s="3">
-        <v>24200</v>
+        <v>23400</v>
       </c>
       <c r="I44" s="3">
-        <v>23400</v>
+        <v>24800</v>
       </c>
       <c r="J44" s="3">
+        <v>24000</v>
+      </c>
+      <c r="K44" s="3">
         <v>24300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>21000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>20100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>17500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>17400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>22900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>27700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>29600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>36000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>38200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>50100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>53300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>39700</v>
+        <v>27900</v>
       </c>
       <c r="E45" s="3">
-        <v>62100</v>
+        <v>40700</v>
       </c>
       <c r="F45" s="3">
-        <v>200600</v>
+        <v>63600</v>
       </c>
       <c r="G45" s="3">
-        <v>74200</v>
+        <v>205800</v>
       </c>
       <c r="H45" s="3">
-        <v>29400</v>
+        <v>76100</v>
       </c>
       <c r="I45" s="3">
-        <v>18400</v>
+        <v>30200</v>
       </c>
       <c r="J45" s="3">
-        <v>100</v>
+        <v>18900</v>
       </c>
       <c r="K45" s="3">
         <v>100</v>
       </c>
       <c r="L45" s="3">
+        <v>100</v>
+      </c>
+      <c r="M45" s="3">
         <v>117500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>118700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>199600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>460600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>469000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>101300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>20500</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
       <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
         <v>1300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>69900</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1585300</v>
+        <v>2321300</v>
       </c>
       <c r="E46" s="3">
-        <v>884700</v>
+        <v>1625700</v>
       </c>
       <c r="F46" s="3">
-        <v>1285800</v>
+        <v>907300</v>
       </c>
       <c r="G46" s="3">
-        <v>785400</v>
+        <v>1318500</v>
       </c>
       <c r="H46" s="3">
-        <v>1216700</v>
+        <v>805400</v>
       </c>
       <c r="I46" s="3">
-        <v>1296100</v>
+        <v>1247600</v>
       </c>
       <c r="J46" s="3">
+        <v>1329100</v>
+      </c>
+      <c r="K46" s="3">
         <v>1534800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1049800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1269100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>845000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>888900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1568200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1034200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>868900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>753600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>816500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1010400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>841200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>114900</v>
+        <v>113000</v>
       </c>
       <c r="E47" s="3">
-        <v>118000</v>
+        <v>117800</v>
       </c>
       <c r="F47" s="3">
-        <v>115800</v>
+        <v>121000</v>
       </c>
       <c r="G47" s="3">
-        <v>125800</v>
+        <v>118800</v>
       </c>
       <c r="H47" s="3">
-        <v>109000</v>
+        <v>129000</v>
       </c>
       <c r="I47" s="3">
-        <v>111100</v>
+        <v>111800</v>
       </c>
       <c r="J47" s="3">
+        <v>113900</v>
+      </c>
+      <c r="K47" s="3">
         <v>218800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>182400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>258300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>279500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>282900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>304700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>308100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>259500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>161300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>60400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>53200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>56400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>16409600</v>
+        <v>17116700</v>
       </c>
       <c r="E48" s="3">
-        <v>16085600</v>
+        <v>16827500</v>
       </c>
       <c r="F48" s="3">
-        <v>15766300</v>
+        <v>16495300</v>
       </c>
       <c r="G48" s="3">
-        <v>15544100</v>
+        <v>16167900</v>
       </c>
       <c r="H48" s="3">
-        <v>15299400</v>
+        <v>15939900</v>
       </c>
       <c r="I48" s="3">
-        <v>15098100</v>
+        <v>15689100</v>
       </c>
       <c r="J48" s="3">
+        <v>15482600</v>
+      </c>
+      <c r="K48" s="3">
         <v>14906000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14587800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14094400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>13064000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13351000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14716000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14984600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13743500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12557600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13084100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12841800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12794300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>12521800</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>163700</v>
+        <v>163400</v>
       </c>
       <c r="E49" s="3">
-        <v>182100</v>
+        <v>167800</v>
       </c>
       <c r="F49" s="3">
-        <v>190700</v>
+        <v>186700</v>
       </c>
       <c r="G49" s="3">
-        <v>205800</v>
+        <v>195500</v>
       </c>
       <c r="H49" s="3">
-        <v>218000</v>
+        <v>211000</v>
       </c>
       <c r="I49" s="3">
-        <v>231700</v>
+        <v>223600</v>
       </c>
       <c r="J49" s="3">
+        <v>237600</v>
+      </c>
+      <c r="K49" s="3">
         <v>225000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>239500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>243300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>237400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>258600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>269600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>272100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>247900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>221400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>211800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>205400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>190800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>157200</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3223,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3171,70 +3288,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>939600</v>
+        <v>826000</v>
       </c>
       <c r="E52" s="3">
-        <v>1318800</v>
+        <v>963500</v>
       </c>
       <c r="F52" s="3">
-        <v>2019700</v>
+        <v>1352400</v>
       </c>
       <c r="G52" s="3">
-        <v>1812700</v>
+        <v>2071200</v>
       </c>
       <c r="H52" s="3">
-        <v>1637100</v>
+        <v>1858900</v>
       </c>
       <c r="I52" s="3">
-        <v>1406700</v>
+        <v>1678800</v>
       </c>
       <c r="J52" s="3">
+        <v>1442500</v>
+      </c>
+      <c r="K52" s="3">
         <v>1684100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1738600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1627300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1021000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>939300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>875600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>903000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1292400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1419300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1357400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1029800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1001800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>669200</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3295,70 +3418,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>19213100</v>
+        <v>20540400</v>
       </c>
       <c r="E54" s="3">
-        <v>18589200</v>
+        <v>19702400</v>
       </c>
       <c r="F54" s="3">
-        <v>19378300</v>
+        <v>19062600</v>
       </c>
       <c r="G54" s="3">
-        <v>18473700</v>
+        <v>19871800</v>
       </c>
       <c r="H54" s="3">
-        <v>18480300</v>
+        <v>18944200</v>
       </c>
       <c r="I54" s="3">
-        <v>18143700</v>
+        <v>18950900</v>
       </c>
       <c r="J54" s="3">
+        <v>18605800</v>
+      </c>
+      <c r="K54" s="3">
         <v>18568700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17798100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>17492400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15446900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15720700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17734000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17501900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16412300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15113300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15530200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>15140700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14884500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14138600</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3381,8 +3510,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3405,380 +3535,399 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>633700</v>
+        <v>542300</v>
       </c>
       <c r="E57" s="3">
-        <v>482000</v>
+        <v>649800</v>
       </c>
       <c r="F57" s="3">
-        <v>505800</v>
+        <v>494300</v>
       </c>
       <c r="G57" s="3">
-        <v>468100</v>
+        <v>518700</v>
       </c>
       <c r="H57" s="3">
-        <v>487000</v>
+        <v>480000</v>
       </c>
       <c r="I57" s="3">
+        <v>499400</v>
+      </c>
+      <c r="J57" s="3">
+        <v>423400</v>
+      </c>
+      <c r="K57" s="3">
+        <v>413800</v>
+      </c>
+      <c r="L57" s="3">
+        <v>423800</v>
+      </c>
+      <c r="M57" s="3">
+        <v>401800</v>
+      </c>
+      <c r="N57" s="3">
+        <v>376200</v>
+      </c>
+      <c r="O57" s="3">
         <v>412900</v>
       </c>
-      <c r="J57" s="3">
-        <v>413800</v>
-      </c>
-      <c r="K57" s="3">
-        <v>423800</v>
-      </c>
-      <c r="L57" s="3">
-        <v>401800</v>
-      </c>
-      <c r="M57" s="3">
-        <v>376200</v>
-      </c>
-      <c r="N57" s="3">
-        <v>412900</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>376000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>484000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>426600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>449800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>445700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>558200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>502000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>572500</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>216800</v>
+        <v>860300</v>
       </c>
       <c r="E58" s="3">
-        <v>225700</v>
+        <v>222300</v>
       </c>
       <c r="F58" s="3">
-        <v>410200</v>
+        <v>231500</v>
       </c>
       <c r="G58" s="3">
-        <v>395100</v>
+        <v>420700</v>
       </c>
       <c r="H58" s="3">
-        <v>845400</v>
+        <v>405200</v>
       </c>
       <c r="I58" s="3">
-        <v>837900</v>
+        <v>867000</v>
       </c>
       <c r="J58" s="3">
+        <v>859200</v>
+      </c>
+      <c r="K58" s="3">
         <v>1092000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1070900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>906400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>820100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>686900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1144900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>919300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>430700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>372400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>612000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1102500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>761200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>120200</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>31900</v>
+        <v>51000</v>
       </c>
       <c r="E59" s="3">
-        <v>29200</v>
+        <v>32700</v>
       </c>
       <c r="F59" s="3">
-        <v>16400</v>
+        <v>29900</v>
       </c>
       <c r="G59" s="3">
-        <v>17900</v>
+        <v>16800</v>
       </c>
       <c r="H59" s="3">
-        <v>20900</v>
+        <v>18400</v>
       </c>
       <c r="I59" s="3">
-        <v>23000</v>
+        <v>21400</v>
       </c>
       <c r="J59" s="3">
+        <v>23600</v>
+      </c>
+      <c r="K59" s="3">
         <v>21800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>32100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>35800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>28300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>35900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>53800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>31200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>43400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>50600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>55600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>882300</v>
+        <v>1453700</v>
       </c>
       <c r="E60" s="3">
-        <v>736900</v>
+        <v>904800</v>
       </c>
       <c r="F60" s="3">
-        <v>932500</v>
+        <v>755700</v>
       </c>
       <c r="G60" s="3">
-        <v>881100</v>
+        <v>956200</v>
       </c>
       <c r="H60" s="3">
-        <v>1353300</v>
+        <v>903600</v>
       </c>
       <c r="I60" s="3">
-        <v>1273900</v>
+        <v>1387800</v>
       </c>
       <c r="J60" s="3">
+        <v>1306300</v>
+      </c>
+      <c r="K60" s="3">
         <v>1527600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1526700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1349400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1232200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1128200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1556800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1445500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>911100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>853400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1101100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1711400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1318800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>786100</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11489900</v>
+        <v>12263600</v>
       </c>
       <c r="E61" s="3">
-        <v>10568300</v>
+        <v>11782500</v>
       </c>
       <c r="F61" s="3">
-        <v>10164200</v>
+        <v>10837500</v>
       </c>
       <c r="G61" s="3">
-        <v>9815900</v>
+        <v>10423100</v>
       </c>
       <c r="H61" s="3">
-        <v>9983600</v>
+        <v>10065900</v>
       </c>
       <c r="I61" s="3">
-        <v>9977100</v>
+        <v>10237900</v>
       </c>
       <c r="J61" s="3">
+        <v>10231200</v>
+      </c>
+      <c r="K61" s="3">
         <v>10355600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9527700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9655900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8334500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8714600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9645800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>9591900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>9322700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8639100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8489500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7822900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7989400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8108900</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4058700</v>
+        <v>4125200</v>
       </c>
       <c r="E62" s="3">
-        <v>4073800</v>
+        <v>4162000</v>
       </c>
       <c r="F62" s="3">
-        <v>4285700</v>
+        <v>4177500</v>
       </c>
       <c r="G62" s="3">
-        <v>3992400</v>
+        <v>4394800</v>
       </c>
       <c r="H62" s="3">
-        <v>3660600</v>
+        <v>4094100</v>
       </c>
       <c r="I62" s="3">
-        <v>3014200</v>
+        <v>3753800</v>
       </c>
       <c r="J62" s="3">
+        <v>3091000</v>
+      </c>
+      <c r="K62" s="3">
         <v>3062500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2989800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>2701600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2236500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2258800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2507100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>2504500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2451800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2332200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2410800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2401100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2370700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2269600</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3839,8 +3988,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3901,8 +4053,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3963,70 +4118,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16430800</v>
+        <v>17842400</v>
       </c>
       <c r="E66" s="3">
-        <v>15379000</v>
+        <v>16849300</v>
       </c>
       <c r="F66" s="3">
-        <v>15382300</v>
+        <v>15770700</v>
       </c>
       <c r="G66" s="3">
-        <v>14689400</v>
+        <v>15774100</v>
       </c>
       <c r="H66" s="3">
-        <v>14997500</v>
+        <v>15063500</v>
       </c>
       <c r="I66" s="3">
-        <v>14265200</v>
+        <v>15379500</v>
       </c>
       <c r="J66" s="3">
+        <v>14628500</v>
+      </c>
+      <c r="K66" s="3">
         <v>14945700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14044200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13706900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11803200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12101500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13709600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13541900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12685500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11824600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>12001300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11935300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11678900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11164700</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4049,8 +4210,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4111,8 +4273,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4173,8 +4338,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4235,8 +4403,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4297,70 +4468,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2134500</v>
+        <v>2062800</v>
       </c>
       <c r="E72" s="3">
-        <v>2536600</v>
+        <v>2188900</v>
       </c>
       <c r="F72" s="3">
-        <v>3068100</v>
+        <v>2601200</v>
       </c>
       <c r="G72" s="3">
-        <v>3030400</v>
+        <v>3146300</v>
       </c>
       <c r="H72" s="3">
-        <v>2788100</v>
+        <v>3107600</v>
       </c>
       <c r="I72" s="3">
-        <v>3226800</v>
+        <v>2859200</v>
       </c>
       <c r="J72" s="3">
+        <v>3309000</v>
+      </c>
+      <c r="K72" s="3">
         <v>2979700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3107900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3161800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3044800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3408200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3341300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3250500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3065400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2671600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2880600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2561100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2555100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2112700</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4421,8 +4598,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4483,8 +4663,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4545,70 +4728,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2782300</v>
+        <v>2698000</v>
       </c>
       <c r="E76" s="3">
-        <v>3210200</v>
+        <v>2853100</v>
       </c>
       <c r="F76" s="3">
-        <v>3996000</v>
+        <v>3291900</v>
       </c>
       <c r="G76" s="3">
-        <v>3784300</v>
+        <v>4097700</v>
       </c>
       <c r="H76" s="3">
-        <v>3482700</v>
+        <v>3880700</v>
       </c>
       <c r="I76" s="3">
-        <v>3878500</v>
+        <v>3571400</v>
       </c>
       <c r="J76" s="3">
+        <v>3977300</v>
+      </c>
+      <c r="K76" s="3">
         <v>3623000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3753900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3785600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3643700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3619200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4024400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3960000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3726700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3288700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3528800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3205300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3205600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2974000</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4669,137 +4858,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43373</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43190</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43008</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42825</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42643</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42460</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42277</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42094</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>149500</v>
+        <v>13300</v>
       </c>
       <c r="E81" s="3">
-        <v>-189500</v>
+        <v>153300</v>
       </c>
       <c r="F81" s="3">
-        <v>451700</v>
+        <v>-194300</v>
       </c>
       <c r="G81" s="3">
-        <v>204000</v>
+        <v>463200</v>
       </c>
       <c r="H81" s="3">
-        <v>-276700</v>
+        <v>209200</v>
       </c>
       <c r="I81" s="3">
-        <v>372900</v>
+        <v>-283700</v>
       </c>
       <c r="J81" s="3">
+        <v>382400</v>
+      </c>
+      <c r="K81" s="3">
         <v>207300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-65600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>196800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>176700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>259200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>214400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>279300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>305500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>249500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>294300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>224200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>142700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4822,70 +5020,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>273100</v>
+        <v>295800</v>
       </c>
       <c r="E83" s="3">
-        <v>277400</v>
+        <v>280000</v>
       </c>
       <c r="F83" s="3">
-        <v>264600</v>
+        <v>284500</v>
       </c>
       <c r="G83" s="3">
-        <v>269600</v>
+        <v>271400</v>
       </c>
       <c r="H83" s="3">
-        <v>265500</v>
+        <v>276500</v>
       </c>
       <c r="I83" s="3">
-        <v>280900</v>
+        <v>272300</v>
       </c>
       <c r="J83" s="3">
+        <v>288000</v>
+      </c>
+      <c r="K83" s="3">
         <v>259500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>359300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>247300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>236800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>233000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>261200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>262200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>246900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>219200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>232900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>241400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>236900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4946,8 +5148,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5008,8 +5213,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5070,8 +5278,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5132,8 +5343,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5194,70 +5408,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>487400</v>
+        <v>477900</v>
       </c>
       <c r="E89" s="3">
-        <v>495100</v>
+        <v>499800</v>
       </c>
       <c r="F89" s="3">
-        <v>512600</v>
+        <v>507700</v>
       </c>
       <c r="G89" s="3">
-        <v>593500</v>
+        <v>525700</v>
       </c>
       <c r="H89" s="3">
-        <v>602200</v>
+        <v>608600</v>
       </c>
       <c r="I89" s="3">
-        <v>589500</v>
+        <v>617500</v>
       </c>
       <c r="J89" s="3">
+        <v>604500</v>
+      </c>
+      <c r="K89" s="3">
         <v>510200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>565500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>451800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>461600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>534600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>551000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>582500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>529800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>516900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>411600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>482600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>444800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5280,70 +5500,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-404200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-359900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-362300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-331700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-340000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-288500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-328600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-315400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-338900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-341100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-374500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-369100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-511600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-457800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-472100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-388000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-436700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-390500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-503400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-456700</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5404,8 +5628,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5466,70 +5693,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-457300</v>
+        <v>-490800</v>
       </c>
       <c r="E94" s="3">
-        <v>-461900</v>
+        <v>-469000</v>
       </c>
       <c r="F94" s="3">
-        <v>-297400</v>
+        <v>-473700</v>
       </c>
       <c r="G94" s="3">
-        <v>-450200</v>
+        <v>-305000</v>
       </c>
       <c r="H94" s="3">
-        <v>-368400</v>
+        <v>-461600</v>
       </c>
       <c r="I94" s="3">
-        <v>-273500</v>
+        <v>-377800</v>
       </c>
       <c r="J94" s="3">
+        <v>-280400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-429400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-364900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-379700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-383100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-366700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-535400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-467800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-566400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-462800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-474500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-408200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-489100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-439100</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5552,70 +5785,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-264800</v>
+        <v>-148400</v>
       </c>
       <c r="E96" s="3">
-        <v>-132400</v>
+        <v>-271500</v>
       </c>
       <c r="F96" s="3">
-        <v>-253000</v>
+        <v>-135800</v>
       </c>
       <c r="G96" s="3">
-        <v>-126600</v>
+        <v>-259400</v>
       </c>
       <c r="H96" s="3">
-        <v>-251600</v>
+        <v>-129800</v>
       </c>
       <c r="I96" s="3">
-        <v>-125700</v>
+        <v>-258000</v>
       </c>
       <c r="J96" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-247900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-122700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-232900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-109900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-220300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-123200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-250000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-116600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-215300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-113900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-223600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-112700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-215700</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5676,8 +5913,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5738,8 +5978,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5800,84 +6043,90 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>29900</v>
+        <v>1331000</v>
       </c>
       <c r="E100" s="3">
-        <v>-277400</v>
+        <v>30700</v>
       </c>
       <c r="F100" s="3">
-        <v>168700</v>
+        <v>-284500</v>
       </c>
       <c r="G100" s="3">
-        <v>-676900</v>
+        <v>172900</v>
       </c>
       <c r="H100" s="3">
-        <v>-359200</v>
+        <v>-694200</v>
       </c>
       <c r="I100" s="3">
-        <v>-501900</v>
+        <v>-368300</v>
       </c>
       <c r="J100" s="3">
+        <v>-514600</v>
+      </c>
+      <c r="K100" s="3">
         <v>387100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-315800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>274700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>25800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-487200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>563400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-323200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>47200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-126000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>65500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>200800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1700</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>5</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
@@ -5891,8 +6140,8 @@
       <c r="K101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5924,66 +6173,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>60000</v>
+        <v>1318100</v>
       </c>
       <c r="E102" s="3">
-        <v>-245900</v>
+        <v>61500</v>
       </c>
       <c r="F102" s="3">
-        <v>383900</v>
+        <v>-252200</v>
       </c>
       <c r="G102" s="3">
-        <v>-531700</v>
+        <v>393700</v>
       </c>
       <c r="H102" s="3">
-        <v>-125400</v>
+        <v>-545200</v>
       </c>
       <c r="I102" s="3">
-        <v>-185800</v>
+        <v>-128600</v>
       </c>
       <c r="J102" s="3">
+        <v>-190500</v>
+      </c>
+      <c r="K102" s="3">
         <v>467800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-115200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>346800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>104200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-319400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>578900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-208600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>10600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>37200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-188900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>139800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>156600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>28800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>UUGRY</t>
   </si>
@@ -656,18 +656,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -682,280 +681,306 @@
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43008</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42825</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42643</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42460</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42277</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42094</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>1269600</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1288600</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1187700</v>
-      </c>
-      <c r="G8" s="3">
-        <v>1206300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1220900</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>1223400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1198800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1144500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1170700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1160800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1056600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1117900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1172600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1239600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1124000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1050600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1138700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1117800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1133500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1131600</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>274100</v>
-      </c>
-      <c r="E9" s="3">
-        <v>277100</v>
-      </c>
-      <c r="F9" s="3">
-        <v>265200</v>
-      </c>
-      <c r="G9" s="3">
-        <v>216600</v>
-      </c>
-      <c r="H9" s="3">
-        <v>205800</v>
-      </c>
-      <c r="I9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K9" s="3">
         <v>169300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>181300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>158500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>164600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>149800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>152600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>161600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>167200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>159600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>153600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>153500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>170600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>162100</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3">
-        <v>995400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1011400</v>
-      </c>
-      <c r="F10" s="3">
-        <v>922500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>989700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1015100</v>
-      </c>
-      <c r="I10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="3">
         <v>1054100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1017500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>985900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1006100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>1011000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>904000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>956300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>1005400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1080000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>970400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>897100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>968100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>955700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -979,8 +1004,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1014,15 +1041,15 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3">
         <v>1400</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1032,20 +1059,26 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T12" s="3">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3">
         <v>3000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1109,138 +1142,156 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="E14" s="3">
-        <v>5500</v>
-      </c>
-      <c r="F14" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-36900</v>
-      </c>
-      <c r="H14" s="3">
-        <v>5500</v>
-      </c>
-      <c r="I14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3">
         <v>4100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>-32000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>3700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>19400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>13400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>59700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>-2900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>15500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>17300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>22200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-13400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>33900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>6400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>11100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>295800</v>
-      </c>
-      <c r="E15" s="3">
-        <v>280000</v>
-      </c>
-      <c r="F15" s="3">
-        <v>284500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>271400</v>
-      </c>
-      <c r="H15" s="3">
-        <v>276300</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3">
         <v>272400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>288000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>259500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>359300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>247300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>236800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>233000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>261200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>262200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>246900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>219200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>232900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>241400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>236900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1261,138 +1312,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>955200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>972900</v>
-      </c>
-      <c r="F17" s="3">
-        <v>948500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>826200</v>
-      </c>
-      <c r="H17" s="3">
-        <v>857100</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>786700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>778500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>736900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>857300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>685500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>710200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>704200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>770800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>756000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>723700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>650900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>760900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>754800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>721600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>314400</v>
-      </c>
-      <c r="E18" s="3">
-        <v>315700</v>
-      </c>
-      <c r="F18" s="3">
-        <v>239200</v>
-      </c>
-      <c r="G18" s="3">
-        <v>380100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>363700</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>436700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>420300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>407600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>313400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>475200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>346500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>413700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>401800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>483700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>400300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>399700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>377700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>363000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>411900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>448400</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1416,333 +1481,365 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-84800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>176100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-153800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>523800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>174700</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>36100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>139600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-16000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-49200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-70200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-25300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>67000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>22900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>63400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>116400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-57000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-75500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>54300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-112200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>525400</v>
-      </c>
-      <c r="E21" s="3">
-        <v>771800</v>
-      </c>
-      <c r="F21" s="3">
-        <v>369900</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1175300</v>
-      </c>
-      <c r="H21" s="3">
-        <v>814900</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>745100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>847900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>651100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>623500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>652300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>558000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>713600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>685800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>809300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>763500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>561900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>535200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>658700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>536600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>648900</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>216500</v>
-      </c>
-      <c r="E22" s="3">
-        <v>281900</v>
-      </c>
-      <c r="F22" s="3">
-        <v>308500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>344600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>240300</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K22" s="3">
         <v>193700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>100800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>134200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>127200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>162900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>114300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>164000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>165800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>204200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>141600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>147500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>122300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>136000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>119400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>13100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>210000</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-223100</v>
-      </c>
-      <c r="G23" s="3">
-        <v>559400</v>
-      </c>
-      <c r="H23" s="3">
-        <v>298100</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>279100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>459100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>257300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>137000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>242100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>206900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>316700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>258800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>342900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>375100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>195100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>179900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>281200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>180300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>269500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E24" s="3">
-        <v>56700</v>
-      </c>
-      <c r="F24" s="3">
-        <v>-28700</v>
-      </c>
-      <c r="G24" s="3">
-        <v>96200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>89000</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>562800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>76800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>50000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>202600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>45300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>30100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>57500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>44500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>63500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>69600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-54400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-114400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>57000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>37500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>55200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1806,138 +1903,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E26" s="3">
-        <v>153300</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-194300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>463200</v>
-      </c>
-      <c r="H26" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>-283700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>382400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>207300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-65600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>196800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>176700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>259200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>214400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>279300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>305500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>249500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>294300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>224200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>142700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E27" s="3">
-        <v>153300</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-194300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>463200</v>
-      </c>
-      <c r="H27" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>-283700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>382400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>207300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-65600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>196800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>176700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>259200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>214400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>279300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>305500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>249500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>294300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>224200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>142700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2001,31 +2116,37 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2048,11 +2169,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>5</v>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -2060,14 +2181,20 @@
       <c r="U29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2131,8 +2258,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2196,138 +2329,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>84800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-176100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>153800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-523800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-174700</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>-36100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-139600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>16000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>49200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>70200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>25300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-67000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-22900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-63400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-116400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>57000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>75500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-54300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>112200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E33" s="3">
-        <v>153300</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-194300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>463200</v>
-      </c>
-      <c r="H33" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>-283700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>382400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>207300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-65600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>196800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>176700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>259200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>214400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>279300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>305500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>249500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>294300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>224200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>142700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2391,143 +2542,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E35" s="3">
-        <v>153300</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-194300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>463200</v>
-      </c>
-      <c r="H35" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>-283700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>382400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>207300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-65600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>196800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>176700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>259200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>214400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>279300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>305500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>249500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>294300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>224200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>142700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43008</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42825</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42643</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42460</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42277</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42094</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2551,8 +2720,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2576,81 +2747,89 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1836200</v>
+        <v>1454100</v>
       </c>
       <c r="E41" s="3">
-        <v>1087600</v>
+        <v>1371100</v>
       </c>
       <c r="F41" s="3">
-        <v>446700</v>
+        <v>1767300</v>
       </c>
       <c r="G41" s="3">
-        <v>698400</v>
+        <v>1782400</v>
       </c>
       <c r="H41" s="3">
-        <v>316100</v>
+        <v>6600</v>
       </c>
       <c r="I41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="J41" s="3">
+        <v>421100</v>
+      </c>
+      <c r="K41" s="3">
         <v>860700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>976400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>1150400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>669300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>771300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>397400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>316700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>695500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>124000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>327300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>292400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>278600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>464900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>321300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>145600</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>976000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>920300</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2659,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1004800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1046400</v>
       </c>
       <c r="J42" s="3">
         <v>0</v>
@@ -2706,463 +2885,511 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>429000</v>
+        <v>561300</v>
       </c>
       <c r="E43" s="3">
-        <v>481100</v>
+        <v>529300</v>
       </c>
       <c r="F43" s="3">
-        <v>379800</v>
+        <v>412900</v>
       </c>
       <c r="G43" s="3">
-        <v>382900</v>
+        <v>416400</v>
       </c>
       <c r="H43" s="3">
-        <v>389900</v>
+        <v>447400</v>
       </c>
       <c r="I43" s="3">
+        <v>465900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>358000</v>
+      </c>
+      <c r="K43" s="3">
         <v>332000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>309800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>360000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>359400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>360200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>311400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>355200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>389200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>413500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>410800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>424900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>479200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>495500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>465200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>464300</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>28200</v>
+        <v>29600</v>
       </c>
       <c r="E44" s="3">
-        <v>16400</v>
+        <v>27900</v>
       </c>
       <c r="F44" s="3">
-        <v>17200</v>
+        <v>27200</v>
       </c>
       <c r="G44" s="3">
-        <v>31500</v>
+        <v>27400</v>
       </c>
       <c r="H44" s="3">
-        <v>23400</v>
+        <v>15300</v>
       </c>
       <c r="I44" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J44" s="3">
+        <v>16200</v>
+      </c>
+      <c r="K44" s="3">
         <v>24800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>24000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>24300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>21000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>20100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>17500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>17400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>22900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>27700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>29600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>36000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>38200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>50100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>53300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>27900</v>
+        <v>19200</v>
       </c>
       <c r="E45" s="3">
-        <v>40700</v>
+        <v>18100</v>
       </c>
       <c r="F45" s="3">
-        <v>63600</v>
+        <v>26900</v>
       </c>
       <c r="G45" s="3">
-        <v>205800</v>
+        <v>27100</v>
       </c>
       <c r="H45" s="3">
-        <v>76100</v>
+        <v>37800</v>
       </c>
       <c r="I45" s="3">
+        <v>39400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>60000</v>
+      </c>
+      <c r="K45" s="3">
         <v>30200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>18900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>117500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>118700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>199600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>460600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>469000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>101300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>20500</v>
       </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+      <c r="X45" s="3">
         <v>1300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>69900</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>2321300</v>
+        <v>3040200</v>
       </c>
       <c r="E46" s="3">
-        <v>1625700</v>
+        <v>2866700</v>
       </c>
       <c r="F46" s="3">
-        <v>907300</v>
+        <v>2234200</v>
       </c>
       <c r="G46" s="3">
-        <v>1318500</v>
+        <v>2253300</v>
       </c>
       <c r="H46" s="3">
-        <v>805400</v>
+        <v>1511800</v>
       </c>
       <c r="I46" s="3">
+        <v>1574400</v>
+      </c>
+      <c r="J46" s="3">
+        <v>855400</v>
+      </c>
+      <c r="K46" s="3">
         <v>1247600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1329100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1534800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1049800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1269100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>845000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>888900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1568200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1034200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>868900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>753600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>816500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1010400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>841200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>113000</v>
+        <v>17400</v>
       </c>
       <c r="E47" s="3">
-        <v>117800</v>
+        <v>16400</v>
       </c>
       <c r="F47" s="3">
-        <v>121000</v>
+        <v>15700</v>
       </c>
       <c r="G47" s="3">
-        <v>118800</v>
+        <v>15800</v>
       </c>
       <c r="H47" s="3">
-        <v>129000</v>
+        <v>18800</v>
       </c>
       <c r="I47" s="3">
+        <v>19600</v>
+      </c>
+      <c r="J47" s="3">
+        <v>20400</v>
+      </c>
+      <c r="K47" s="3">
         <v>111800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>113900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>218800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>182400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>258300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>279500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>282900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>304700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>308100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>259500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>161300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>60400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>53200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>56400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17116700</v>
+        <v>17937700</v>
       </c>
       <c r="E48" s="3">
-        <v>16827500</v>
+        <v>16913700</v>
       </c>
       <c r="F48" s="3">
-        <v>16495300</v>
+        <v>16474700</v>
       </c>
       <c r="G48" s="3">
-        <v>16167900</v>
+        <v>16615200</v>
       </c>
       <c r="H48" s="3">
-        <v>15939900</v>
+        <v>15649200</v>
       </c>
       <c r="I48" s="3">
+        <v>16296500</v>
+      </c>
+      <c r="J48" s="3">
+        <v>15551600</v>
+      </c>
+      <c r="K48" s="3">
         <v>15689100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>15482600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14906000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>14587800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>14094400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>13064000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>13351000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>14716000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14984600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>13743500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>12557600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13084100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>12841800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>12794300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>12521800</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>163400</v>
+        <v>155200</v>
       </c>
       <c r="E49" s="3">
-        <v>167800</v>
+        <v>146300</v>
       </c>
       <c r="F49" s="3">
-        <v>186700</v>
+        <v>157200</v>
       </c>
       <c r="G49" s="3">
-        <v>195500</v>
+        <v>158600</v>
       </c>
       <c r="H49" s="3">
-        <v>211000</v>
+        <v>156100</v>
       </c>
       <c r="I49" s="3">
+        <v>162500</v>
+      </c>
+      <c r="J49" s="3">
+        <v>176000</v>
+      </c>
+      <c r="K49" s="3">
         <v>223600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>237600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>225000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>239500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>243300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>237400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>258600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>269600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>272100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>247900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>221400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>211800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>205400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>190800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>157200</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3226,8 +3453,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3291,73 +3524,85 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>826000</v>
+        <v>809500</v>
       </c>
       <c r="E52" s="3">
-        <v>963500</v>
+        <v>763300</v>
       </c>
       <c r="F52" s="3">
-        <v>1352400</v>
+        <v>795000</v>
       </c>
       <c r="G52" s="3">
-        <v>2071200</v>
+        <v>801800</v>
       </c>
       <c r="H52" s="3">
-        <v>1858900</v>
+        <v>896100</v>
       </c>
       <c r="I52" s="3">
+        <v>933100</v>
+      </c>
+      <c r="J52" s="3">
+        <v>1275000</v>
+      </c>
+      <c r="K52" s="3">
         <v>1678800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1442500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1684100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1738600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1627300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1021000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>939300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>875600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>903000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1292400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1419300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1357400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1029800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1001800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>669200</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3421,73 +3666,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20540400</v>
+        <v>22057100</v>
       </c>
       <c r="E54" s="3">
-        <v>19702400</v>
+        <v>20798000</v>
       </c>
       <c r="F54" s="3">
-        <v>19062600</v>
+        <v>19769900</v>
       </c>
       <c r="G54" s="3">
-        <v>19871800</v>
+        <v>19938600</v>
       </c>
       <c r="H54" s="3">
-        <v>18944200</v>
+        <v>18322800</v>
       </c>
       <c r="I54" s="3">
+        <v>19080700</v>
+      </c>
+      <c r="J54" s="3">
+        <v>17972100</v>
+      </c>
+      <c r="K54" s="3">
         <v>18950900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>18605800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18568700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>17798100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>17492400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>15446900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>15720700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>17734000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>17501900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>16412300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>15113300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>15530200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15140700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>14884500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>14138600</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3511,8 +3768,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3536,398 +3795,436 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>542300</v>
+        <v>716800</v>
       </c>
       <c r="E57" s="3">
-        <v>649800</v>
+        <v>675900</v>
       </c>
       <c r="F57" s="3">
-        <v>494300</v>
+        <v>29600</v>
       </c>
       <c r="G57" s="3">
-        <v>518700</v>
+        <v>29800</v>
       </c>
       <c r="H57" s="3">
-        <v>480000</v>
+        <v>604300</v>
       </c>
       <c r="I57" s="3">
+        <v>629300</v>
+      </c>
+      <c r="J57" s="3">
+        <v>32700</v>
+      </c>
+      <c r="K57" s="3">
         <v>499400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>423400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>413800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>423800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>401800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>376200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>412900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>376000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>484000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>426600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>449800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>445700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>558200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>502000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>572500</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>860300</v>
+        <v>933800</v>
       </c>
       <c r="E58" s="3">
-        <v>222300</v>
+        <v>880500</v>
       </c>
       <c r="F58" s="3">
-        <v>231500</v>
+        <v>828000</v>
       </c>
       <c r="G58" s="3">
-        <v>420700</v>
+        <v>835100</v>
       </c>
       <c r="H58" s="3">
-        <v>405200</v>
+        <v>206700</v>
       </c>
       <c r="I58" s="3">
+        <v>215300</v>
+      </c>
+      <c r="J58" s="3">
+        <v>218200</v>
+      </c>
+      <c r="K58" s="3">
         <v>867000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>859200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1092000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1070900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>906400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>820100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>686900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1144900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>919300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>430700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>372400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>612000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>1102500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>761200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>120200</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>51000</v>
+        <v>50400</v>
       </c>
       <c r="E59" s="3">
-        <v>32700</v>
+        <v>47500</v>
       </c>
       <c r="F59" s="3">
-        <v>29900</v>
+        <v>143200</v>
       </c>
       <c r="G59" s="3">
-        <v>16800</v>
+        <v>144400</v>
       </c>
       <c r="H59" s="3">
-        <v>18400</v>
+        <v>30400</v>
       </c>
       <c r="I59" s="3">
+        <v>31600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>124100</v>
+      </c>
+      <c r="K59" s="3">
         <v>21400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>23600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>21800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>32100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>41200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>35800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>28300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>35900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>42300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>53800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>31200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>43400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>50600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>55600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1453700</v>
+        <v>1701000</v>
       </c>
       <c r="E60" s="3">
-        <v>904800</v>
+        <v>1603900</v>
       </c>
       <c r="F60" s="3">
-        <v>755700</v>
+        <v>1399100</v>
       </c>
       <c r="G60" s="3">
-        <v>956200</v>
+        <v>1411100</v>
       </c>
       <c r="H60" s="3">
-        <v>903600</v>
+        <v>841400</v>
       </c>
       <c r="I60" s="3">
+        <v>876200</v>
+      </c>
+      <c r="J60" s="3">
+        <v>712500</v>
+      </c>
+      <c r="K60" s="3">
         <v>1387800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1306300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1527600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1526700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1349400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1232200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1128200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1556800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1445500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>911100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>853400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1101100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1711400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1318800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>786100</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>12263600</v>
+        <v>13404600</v>
       </c>
       <c r="E61" s="3">
-        <v>11782500</v>
+        <v>12639400</v>
       </c>
       <c r="F61" s="3">
-        <v>10837500</v>
+        <v>11803500</v>
       </c>
       <c r="G61" s="3">
-        <v>10423100</v>
+        <v>11904300</v>
       </c>
       <c r="H61" s="3">
-        <v>10065900</v>
+        <v>10957500</v>
       </c>
       <c r="I61" s="3">
+        <v>11410700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>10217500</v>
+      </c>
+      <c r="K61" s="3">
         <v>10237900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10231200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10355600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>9527700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>9655900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>8334500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8714600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>9645800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>9591900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9322700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>8639100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>8489500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>7822900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>7989400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>8108900</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4125200</v>
+        <v>1711800</v>
       </c>
       <c r="E62" s="3">
-        <v>4162000</v>
+        <v>1614100</v>
       </c>
       <c r="F62" s="3">
-        <v>4177500</v>
+        <v>347800</v>
       </c>
       <c r="G62" s="3">
-        <v>4394800</v>
+        <v>350800</v>
       </c>
       <c r="H62" s="3">
-        <v>4094100</v>
+        <v>1473700</v>
       </c>
       <c r="I62" s="3">
+        <v>1534600</v>
+      </c>
+      <c r="J62" s="3">
+        <v>324400</v>
+      </c>
+      <c r="K62" s="3">
         <v>3753800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3091000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3062500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2989800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2701600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2236500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2258800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2507100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2504500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2451800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2332200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2410800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2401100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2370700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2269600</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3991,8 +4288,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4056,8 +4359,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4121,73 +4430,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17842400</v>
+        <v>19459100</v>
       </c>
       <c r="E66" s="3">
-        <v>16849300</v>
+        <v>18348200</v>
       </c>
       <c r="F66" s="3">
-        <v>15770700</v>
+        <v>17173100</v>
       </c>
       <c r="G66" s="3">
-        <v>15774100</v>
+        <v>17319600</v>
       </c>
       <c r="H66" s="3">
-        <v>15063500</v>
+        <v>15669500</v>
       </c>
       <c r="I66" s="3">
+        <v>16317600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>14868500</v>
+      </c>
+      <c r="K66" s="3">
         <v>15379500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14628500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>14945700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14044200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>13706900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>11803200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>12101500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>13709600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>13541900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12685500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>11824600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12001300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11935300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>11678900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11164700</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4211,8 +4532,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4276,8 +4599,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4341,8 +4670,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4406,8 +4741,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4471,73 +4812,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2062800</v>
+        <v>1504200</v>
       </c>
       <c r="E72" s="3">
-        <v>2188900</v>
+        <v>1418400</v>
       </c>
       <c r="F72" s="3">
-        <v>2601200</v>
+        <v>1569000</v>
       </c>
       <c r="G72" s="3">
-        <v>3146300</v>
+        <v>1582400</v>
       </c>
       <c r="H72" s="3">
-        <v>3107600</v>
+        <v>1633300</v>
       </c>
       <c r="I72" s="3">
+        <v>1700800</v>
+      </c>
+      <c r="J72" s="3">
+        <v>2044500</v>
+      </c>
+      <c r="K72" s="3">
         <v>2859200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3309000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2979700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3107900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3161800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3044800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3408200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3341300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3250500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3065400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>2671600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>2880600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2561100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2555100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2112700</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4601,8 +4954,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4666,8 +5025,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4731,73 +5096,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>2698000</v>
+        <v>2598000</v>
       </c>
       <c r="E76" s="3">
-        <v>2853100</v>
+        <v>2449700</v>
       </c>
       <c r="F76" s="3">
-        <v>3291900</v>
+        <v>2596800</v>
       </c>
       <c r="G76" s="3">
-        <v>4097700</v>
+        <v>2619000</v>
       </c>
       <c r="H76" s="3">
-        <v>3880700</v>
+        <v>2653300</v>
       </c>
       <c r="I76" s="3">
+        <v>2763100</v>
+      </c>
+      <c r="J76" s="3">
+        <v>3103600</v>
+      </c>
+      <c r="K76" s="3">
         <v>3571400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3977300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3623000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3753900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3785600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3643700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3619200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4024400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3960000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>3726700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3288700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3528800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3205300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3205600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>2974000</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4861,143 +5238,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43008</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42825</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42643</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42460</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42277</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42094</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>13300</v>
-      </c>
-      <c r="E81" s="3">
-        <v>153300</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-194300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>463200</v>
-      </c>
-      <c r="H81" s="3">
-        <v>209200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>-283700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>382400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>207300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-65600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>196800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>176700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>259200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>214400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>279300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>305500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>249500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>294300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>224200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>142700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5021,73 +5416,81 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>295800</v>
+        <v>119500</v>
       </c>
       <c r="E83" s="3">
-        <v>280000</v>
+        <v>124500</v>
       </c>
       <c r="F83" s="3">
-        <v>284500</v>
+        <v>122900</v>
       </c>
       <c r="G83" s="3">
-        <v>271400</v>
+        <v>119700</v>
       </c>
       <c r="H83" s="3">
-        <v>276500</v>
+        <v>104100</v>
       </c>
       <c r="I83" s="3">
+        <v>113500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>125000</v>
+      </c>
+      <c r="K83" s="3">
         <v>272300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>288000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>259500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>359300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>247300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>236800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>233000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>261200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>262200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>246900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>219200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>232900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>241400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>236900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5151,8 +5554,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5216,8 +5625,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5281,8 +5696,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5346,8 +5767,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5411,73 +5838,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>477900</v>
+        <v>317200</v>
       </c>
       <c r="E89" s="3">
-        <v>499800</v>
+        <v>299100</v>
       </c>
       <c r="F89" s="3">
-        <v>507700</v>
+        <v>230000</v>
       </c>
       <c r="G89" s="3">
-        <v>525700</v>
+        <v>232000</v>
       </c>
       <c r="H89" s="3">
-        <v>608600</v>
+        <v>232400</v>
       </c>
       <c r="I89" s="3">
+        <v>242000</v>
+      </c>
+      <c r="J89" s="3">
+        <v>239300</v>
+      </c>
+      <c r="K89" s="3">
         <v>617500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>604500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>510200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>565500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>451800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>461600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>534600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>551000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>582500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>529800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>516900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>411600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>482600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>444800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5501,73 +5940,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-404200</v>
+        <v>-292200</v>
       </c>
       <c r="E91" s="3">
-        <v>-359900</v>
+        <v>-275500</v>
       </c>
       <c r="F91" s="3">
-        <v>-362300</v>
+        <v>-248000</v>
       </c>
       <c r="G91" s="3">
-        <v>-331700</v>
+        <v>-250100</v>
       </c>
       <c r="H91" s="3">
-        <v>-340000</v>
+        <v>-217700</v>
       </c>
       <c r="I91" s="3">
+        <v>-226700</v>
+      </c>
+      <c r="J91" s="3">
+        <v>-218000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-288500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-328600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-315400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-338900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-341100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-374500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-369100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-511600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-457800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-472100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-388000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-436700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-390500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-503400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-456700</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5631,8 +6078,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5696,73 +6149,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-490800</v>
+        <v>-782600</v>
       </c>
       <c r="E94" s="3">
-        <v>-469000</v>
+        <v>-737900</v>
       </c>
       <c r="F94" s="3">
-        <v>-473700</v>
+        <v>-236200</v>
       </c>
       <c r="G94" s="3">
-        <v>-305000</v>
+        <v>-238200</v>
       </c>
       <c r="H94" s="3">
-        <v>-461600</v>
+        <v>-489600</v>
       </c>
       <c r="I94" s="3">
+        <v>-509800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-223300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-377800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-280400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-429400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-364900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-379700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-383100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-366700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-535400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-467800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-566400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-462800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-474500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-408200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-489100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-439100</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5786,73 +6251,81 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-148400</v>
+        <v>151700</v>
       </c>
       <c r="E96" s="3">
-        <v>-271500</v>
+        <v>143000</v>
       </c>
       <c r="F96" s="3">
-        <v>-135800</v>
+        <v>71400</v>
       </c>
       <c r="G96" s="3">
-        <v>-259400</v>
+        <v>72000</v>
       </c>
       <c r="H96" s="3">
-        <v>-129800</v>
+        <v>126200</v>
       </c>
       <c r="I96" s="3">
+        <v>131500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>64000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-258000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-128900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-247900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-122700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-232900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-109900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-220300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-123200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-250000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-116600</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-215300</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-113900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-223600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-112700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-215700</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5916,8 +6389,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5981,8 +6460,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6046,87 +6531,99 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1331000</v>
+        <v>261200</v>
       </c>
       <c r="E100" s="3">
-        <v>30700</v>
+        <v>246200</v>
       </c>
       <c r="F100" s="3">
-        <v>-284500</v>
+        <v>640500</v>
       </c>
       <c r="G100" s="3">
-        <v>172900</v>
+        <v>646000</v>
       </c>
       <c r="H100" s="3">
-        <v>-694200</v>
+        <v>285800</v>
       </c>
       <c r="I100" s="3">
+        <v>297600</v>
+      </c>
+      <c r="J100" s="3">
+        <v>-134100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-368300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-514600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>387100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-315800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>274700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>25800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-487200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>563400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-323200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>47200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-16900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-126000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>65500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>200800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="F101" s="3">
-        <v>-1700</v>
+        <v>-800</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>5</v>
@@ -6134,8 +6631,8 @@
       <c r="I101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
+      <c r="J101" s="3">
+        <v>1000</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>5</v>
@@ -6143,11 +6640,11 @@
       <c r="L101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O101" s="3">
         <v>0</v>
@@ -6176,69 +6673,81 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1318100</v>
+        <v>-204300</v>
       </c>
       <c r="E102" s="3">
-        <v>61500</v>
+        <v>-192600</v>
       </c>
       <c r="F102" s="3">
-        <v>-252200</v>
+        <v>634300</v>
       </c>
       <c r="G102" s="3">
-        <v>393700</v>
+        <v>639700</v>
       </c>
       <c r="H102" s="3">
-        <v>-545200</v>
+        <v>28600</v>
       </c>
       <c r="I102" s="3">
+        <v>29800</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-118900</v>
+      </c>
+      <c r="K102" s="3">
         <v>-128600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-190500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>467800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-115200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>346800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>104200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-319400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>578900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-208600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>10600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>37200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-188900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>139800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>156600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>28800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
   <si>
     <t>UUGRY</t>
   </si>
@@ -656,19 +656,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -683,91 +682,99 @@
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43373</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43190</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43008</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42825</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42643</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42460</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42277</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42094</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -792,53 +799,59 @@
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>1223400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1198800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1144500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1170700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1160800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1056600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>1117900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1172600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>1239600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>1124000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>1050600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>1138700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>1117800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>1133500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>1131600</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -863,53 +876,59 @@
       <c r="J9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>169300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>181300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>158500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>164600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>149800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>152600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>161600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>167200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>159600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>153600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>153500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>170600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>162100</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,53 +953,59 @@
       <c r="J10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M10" s="3">
         <v>1054100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>1017500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>985900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1006100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>1011000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>904000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>956300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>1005400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1080000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>970400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>897100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>968100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>955700</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1006,8 +1031,10 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1047,15 +1074,15 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3">
         <v>1400</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1065,20 +1092,26 @@
       <c r="U12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V12" s="3">
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X12" s="3">
         <v>3000</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1148,8 +1181,14 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1174,53 +1213,59 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3">
         <v>4100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>-32000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>3700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>19400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>13400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>59700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-2900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>15500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>17300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>22200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-13400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>33900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>6400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>11100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1245,53 +1290,59 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
         <v>272400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>288000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>259500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>359300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>247300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>236800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>233000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>261200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>262200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>246900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>219200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>232900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>241400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>236900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1314,8 +1365,10 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1340,53 +1393,59 @@
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>786700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>778500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>736900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>857300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>685500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>710200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>704200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>770800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>756000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>723700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>650900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>760900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>754800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>721600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>683300</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1411,53 +1470,59 @@
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>436700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>420300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>407600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>313400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>475200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>346500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>413700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>401800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>483700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>400300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>399700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>377700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>363000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>411900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>448400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1483,8 +1548,10 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1509,53 +1576,59 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>36100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>139600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-16000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-49200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-70200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-25300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>67000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>22900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>63400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>116400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-57000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-75500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>54300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-112200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-26900</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1580,53 +1653,59 @@
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>745100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>847900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>651100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>623500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>652300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>558000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>713600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>685800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>809300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>763500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>561900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>535200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>658700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>536600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>648900</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1651,53 +1730,59 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22" s="3">
         <v>193700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>100800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>134200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>127200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>162900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>114300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>164000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>165800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>204200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>141600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>147500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>122300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>136000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>119400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1722,53 +1807,59 @@
       <c r="J23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>279100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>459100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>257300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>137000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>242100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>206900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>316700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>258800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>342900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>375100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>195100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>179900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>281200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>180300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>269500</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1793,53 +1884,59 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>562800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>76800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>50000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>202600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>45300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>30100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>57500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>44500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>63500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>69600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-54400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-114400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>57000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>37500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>55200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1909,8 +2006,14 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1935,53 +2038,59 @@
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>-283700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>382400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>207300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-65600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>196800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>176700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>259200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>214400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>279300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>305500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>249500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>294300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>224200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>142700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2006,53 +2115,59 @@
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>-283700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>382400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>207300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-65600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>196800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>176700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>259200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>214400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>279300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>305500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>249500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>294300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>224200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>142700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2122,8 +2237,14 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2148,11 +2269,11 @@
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2175,11 +2296,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2187,14 +2308,20 @@
       <c r="W29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2264,8 +2391,14 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2335,8 +2468,14 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2361,53 +2500,59 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>-36100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-139600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>16000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>49200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>70200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>25300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-67000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-22900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-63400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-116400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>57000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>75500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-54300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>112200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>26900</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2432,53 +2577,59 @@
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>-283700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>382400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>207300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-65600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>196800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>176700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>259200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>214400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>279300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>305500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>249500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>294300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>224200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>142700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2548,8 +2699,14 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2574,129 +2731,141 @@
       <c r="J35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>-283700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>382400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>207300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-65600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>196800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>176700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>259200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>214400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>279300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>305500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>249500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>294300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>224200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>142700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43373</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43190</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43008</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42825</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42643</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42460</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42277</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42094</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2722,8 +2891,10 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2749,106 +2920,114 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2161000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2094000</v>
+      </c>
+      <c r="F41" s="3">
         <v>1454100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1371100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1767300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1782400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>6600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>6900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>421100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>860700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>976400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1150400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>669300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>771300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>397400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>316700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>695500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>124000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>327300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>292400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>278600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>464900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>321300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>145600</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>976000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>920300</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>1004800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>1046400</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2891,505 +3070,553 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>484900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>469800</v>
+      </c>
+      <c r="F43" s="3">
         <v>561300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>529300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>412900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>416400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>447400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>465900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>358000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>332000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>309800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>360000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>359400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>360200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>311400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>355200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>389200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>413500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>410800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>424900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>479200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>495500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>465200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>464300</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F44" s="3">
         <v>29600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>27900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>27200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>27400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>15300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>15900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>16200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>24800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>24000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>24300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>21000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>20100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>17500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>17400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>22900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>27700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>29600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>36000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>38200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>50100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>53300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>53600</v>
       </c>
     </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14300</v>
+      </c>
+      <c r="F45" s="3">
         <v>19200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>18100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>26900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>27100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>37800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>39400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>60000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>30200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>18900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>117500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>118700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>199600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>460600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>469000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>101300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>20500</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="3">
         <v>1300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>69900</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2692400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2608900</v>
+      </c>
+      <c r="F46" s="3">
         <v>3040200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>2866700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>2234200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>2253300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1511800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1574400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>855400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1247600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1329100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1534800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1049800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1269100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>845000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>888900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1568200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1034200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>868900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>753600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>816500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1010400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>841200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>733500</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E47" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F47" s="3">
         <v>17400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>16400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>15700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>15800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>18800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>19600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>20400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>111800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>113900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>218800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>182400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>258300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>279500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>282900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>304700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>308100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>259500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>161300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>60400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>53200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>56400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17924000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>17368000</v>
+      </c>
+      <c r="F48" s="3">
         <v>17937700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>16913700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>16474700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>16615200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>15649200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>16296500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>15551600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>15689100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>15482600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>14906000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>14587800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>14094400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>13064000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>13351000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14716000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>14984600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>13743500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>12557600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>13084100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>12841800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>12794300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>12521800</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>136700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>132500</v>
+      </c>
+      <c r="F49" s="3">
         <v>155200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>146300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>157200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>158600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>156100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>162500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>176000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>223600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>237600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>225000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>239500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>243300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>237400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>258600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>269600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>272100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>247900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>221400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>211800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>205400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>190800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>157200</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3459,8 +3686,14 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3530,79 +3763,91 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>816000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>790700</v>
+      </c>
+      <c r="F52" s="3">
         <v>809500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>763300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>795000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>801800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>896100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>933100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1275000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1678800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1442500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1684100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1738600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1627300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1021000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>939300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>875600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>903000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>1292400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1419300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1357400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>1029800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1001800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>669200</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3672,79 +3917,91 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>21666300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>20994200</v>
+      </c>
+      <c r="F54" s="3">
         <v>22057100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>20798000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>19769900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19938600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>18322800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>19080700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>17972100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>18950900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>18605800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>18568700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>17798100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>17492400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>15446900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>15720700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>17734000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>17501900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>16412300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>15113300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>15530200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>15140700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>14884500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>14138600</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3770,8 +4027,10 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3797,434 +4056,472 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>745700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>722600</v>
+      </c>
+      <c r="F57" s="3">
         <v>716800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>675900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>29600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>29800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>604300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>629300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>32700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>499400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>423400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>413800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>423800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>401800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>376200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>412900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>376000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>484000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>426600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>449800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>445700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>558200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>502000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>572500</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>597000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>578500</v>
+      </c>
+      <c r="F58" s="3">
         <v>933800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>880500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>828000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>835100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>206700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>215300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>218200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>867000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>859200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1092000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1070900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>906400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>820100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>686900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>1144900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>919300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>430700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>372400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>612000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>1102500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>761200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>120200</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>47300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>45800</v>
+      </c>
+      <c r="F59" s="3">
         <v>50400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>47500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>143200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>144400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>30400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>31600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>124100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>21400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>23600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>21800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>32100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>41200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>35800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>28300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>35900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>42300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>53800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>31200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>43400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>50600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>55600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>93400</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1390100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1346900</v>
+      </c>
+      <c r="F60" s="3">
         <v>1701000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1603900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1399100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1411100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>841400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>876200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>712500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1387800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1306300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1527600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1526700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1349400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1232200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>1128200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1556800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1445500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>911100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>853400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1101100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>1711400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>1318800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>786100</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13341900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>12928000</v>
+      </c>
+      <c r="F61" s="3">
         <v>13404600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>12639400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>11803500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11904300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>10957500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>11410700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>10217500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>10237900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>10231200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>10355600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>9527700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>9655900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8334500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8714600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>9645800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>9591900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>9322700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>8639100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>8489500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>7822900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>7989400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>8108900</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1729700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1676100</v>
+      </c>
+      <c r="F62" s="3">
         <v>1711800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>1614100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>347800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>350800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>1473700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1534600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>324400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3753800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3091000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3062500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2989800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2701600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2236500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2258800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2507100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2504500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>2451800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>2332200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>2410800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>2401100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>2370700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>2269600</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4294,8 +4591,14 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4365,8 +4668,14 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4436,79 +4745,91 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>19082400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>18490400</v>
+      </c>
+      <c r="F66" s="3">
         <v>19459100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>18348200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>17173100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>17319600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>15669500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>16317600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>14868500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>15379500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14628500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14945700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>14044200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>13706900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>11803200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>12101500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>13709600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>13541900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>12685500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>11824600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>12001300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>11935300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>11678900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>11164700</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4534,8 +4855,10 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4605,8 +4928,14 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4676,8 +5005,14 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4747,8 +5082,14 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4818,79 +5159,91 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1522000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1474800</v>
+      </c>
+      <c r="F72" s="3">
         <v>1504200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1418400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1569000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1582400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1633300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1700800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2044500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2859200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3309000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2979700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3107900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3161800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3044800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>3408200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3341300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>3250500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>3065400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>2671600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>2880600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>2561100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>2555100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>2112700</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4960,8 +5313,14 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5031,8 +5390,14 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5102,79 +5467,91 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2583900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>2503700</v>
+      </c>
+      <c r="F76" s="3">
         <v>2598000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>2449700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>2596800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>2619000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>2653300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>2763100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3103600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3571400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>3977300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>3623000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>3753900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>3785600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>3643700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>3619200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>4024400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>3960000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>3726700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>3288700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>3528800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>3205300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>3205600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>2974000</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5244,84 +5621,96 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43373</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43190</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43008</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42825</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42643</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42460</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42277</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42094</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>41912</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5346,53 +5735,59 @@
       <c r="J81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>-283700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>382400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>207300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-65600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>196800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>176700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>259200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>214400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>279300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>305500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>249500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>294300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>224200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>142700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5418,79 +5813,87 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>132700</v>
+      </c>
+      <c r="E83" s="3">
+        <v>133900</v>
+      </c>
+      <c r="F83" s="3">
         <v>119500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>124500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>122900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>119700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>104100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>113500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>125000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>272300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>288000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>259500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>359300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>247300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>236800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>233000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>261200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>262200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>246900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>219200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>232900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>241400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>236900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>227400</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5560,8 +5963,14 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5631,8 +6040,14 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5702,8 +6117,14 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5773,8 +6194,14 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5844,79 +6271,91 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>287300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>278400</v>
+      </c>
+      <c r="F89" s="3">
         <v>317200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>299100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>230000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>232000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>232400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>242000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>239300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>617500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>604500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>510200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>565500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>451800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>461600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>534600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>551000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>582500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>529800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>516900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>411600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>482600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>444800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>485500</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5942,79 +6381,87 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-356900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-345800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-292200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-275500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-248000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-250100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-217700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-226700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-218000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-288500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-328600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-315400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-338900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-341100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-374500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-369100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-511600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-457800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-472100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-388000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-436700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-390500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-503400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-456700</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6084,8 +6531,14 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6155,79 +6608,91 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>116700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>113000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-782600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-737900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-236200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-238200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-489600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-509800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-223300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-377800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-280400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-429400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-364900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-379700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-383100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-366700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-535400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-467800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-566400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-462800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-474500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-408200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-489100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-439100</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6253,79 +6718,87 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>73700</v>
+      </c>
+      <c r="F96" s="3">
         <v>151700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>143000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>71400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>72000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>126200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>131500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>64000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-258000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-128900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-247900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-122700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-232900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-109900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-220300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-123200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-250000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-116600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-215300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-113900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-223600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-112700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-215700</v>
       </c>
     </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6395,8 +6868,14 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6466,8 +6945,14 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6537,79 +7022,91 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="F100" s="3">
         <v>261200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>246200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>640500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>646000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>285800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>297600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-134100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-368300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-514600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>387100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-315800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>274700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>25800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-487200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>563400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-323200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>47200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-16900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-126000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>65500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>200800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-17500</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6619,38 +7116,38 @@
       <c r="E101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F101" s="3">
+      <c r="F101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>1000</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6679,75 +7176,87 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>384000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>372100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-204300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-192600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>634300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>639700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>28600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>29800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-118900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-128600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-190500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>467800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-115200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>346800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>104200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-319400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>578900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-208600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>10600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>37200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-188900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>139800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>156600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>28800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/UUGRY_QTR_FIN.xlsx
@@ -3775,10 +3775,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>816000</v>
+        <v>816200</v>
       </c>
       <c r="E52" s="3">
-        <v>790700</v>
+        <v>790800</v>
       </c>
       <c r="F52" s="3">
         <v>809500</v>
@@ -3929,10 +3929,10 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21666300</v>
+        <v>21666400</v>
       </c>
       <c r="E54" s="3">
-        <v>20994200</v>
+        <v>20994300</v>
       </c>
       <c r="F54" s="3">
         <v>22057100</v>
@@ -4064,10 +4064,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>745700</v>
+        <v>38600</v>
       </c>
       <c r="E57" s="3">
-        <v>722600</v>
+        <v>37400</v>
       </c>
       <c r="F57" s="3">
         <v>716800</v>
@@ -4218,10 +4218,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>47300</v>
+        <v>168900</v>
       </c>
       <c r="E59" s="3">
-        <v>45800</v>
+        <v>163600</v>
       </c>
       <c r="F59" s="3">
         <v>50400</v>
@@ -4372,10 +4372,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>13341900</v>
+        <v>13342000</v>
       </c>
       <c r="E61" s="3">
-        <v>12928000</v>
+        <v>12928100</v>
       </c>
       <c r="F61" s="3">
         <v>13404600</v>
@@ -4449,10 +4449,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1729700</v>
+        <v>378400</v>
       </c>
       <c r="E62" s="3">
-        <v>1676100</v>
+        <v>366700</v>
       </c>
       <c r="F62" s="3">
         <v>1711800</v>
@@ -4757,10 +4757,10 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>19082400</v>
+        <v>19082500</v>
       </c>
       <c r="E66" s="3">
-        <v>18490400</v>
+        <v>18490600</v>
       </c>
       <c r="F66" s="3">
         <v>19459100</v>
@@ -6632,10 +6632,10 @@
         <v>-737900</v>
       </c>
       <c r="H94" s="3">
-        <v>-236200</v>
+        <v>44800</v>
       </c>
       <c r="I94" s="3">
-        <v>-238200</v>
+        <v>45200</v>
       </c>
       <c r="J94" s="3">
         <v>-489600</v>
@@ -7046,10 +7046,10 @@
         <v>246200</v>
       </c>
       <c r="H100" s="3">
-        <v>640500</v>
+        <v>359500</v>
       </c>
       <c r="I100" s="3">
-        <v>646000</v>
+        <v>362600</v>
       </c>
       <c r="J100" s="3">
         <v>285800</v>
